--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.2 Épicas e Historias de Usuario/Historias Usuario con instructivo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.2 Épicas e Historias de Usuario/Historias Usuario con instructivo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="182">
   <si>
     <t>Desarrollo ágil: Historias de usuario y criterios de aceptación</t>
   </si>
@@ -521,6 +521,51 @@
   <si>
     <t xml:space="preserve">Generar un CRUD de los datos de compra de los usuarios </t>
   </si>
+  <si>
+    <t>EP-05/HU-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuario que activó una alerta (o usuario apadrinado) </t>
+  </si>
+  <si>
+    <t>quiero finalizar una alerta generada</t>
+  </si>
+  <si>
+    <t>para que mis contactos sepan que la situación terminó y se revoque el acceso a mi información medica</t>
+  </si>
+  <si>
+    <t>Finalizar emergencia</t>
+  </si>
+  <si>
+    <t>El usuario tiene una alerta ACTIVA y ya puede finalizar la misma por su propia cuenta</t>
+  </si>
+  <si>
+    <t>Expiración automatica</t>
+  </si>
+  <si>
+    <t>Tarea automatica</t>
+  </si>
+  <si>
+    <t>Emergencia ya cerrada</t>
+  </si>
+  <si>
+    <t>Alerta finalizada</t>
+  </si>
+  <si>
+    <t>EP-02/HU-15</t>
+  </si>
+  <si>
+    <t>EP-07/HU-16</t>
+  </si>
+  <si>
+    <t>EP-04/HU-17</t>
+  </si>
+  <si>
+    <t>EP-09/HU-18</t>
+  </si>
+  <si>
+    <t>EP-09/HU-19</t>
+  </si>
 </sst>
 </file>
 
@@ -594,7 +639,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left/>
@@ -608,11 +653,6 @@
       <bottom/>
     </border>
     <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <right/>
       <top/>
       <bottom/>
     </border>
@@ -704,7 +744,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -715,44 +755,54 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="7" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -993,7 +1043,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
+      <c r="I1" s="3"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1014,7 +1064,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1"/>
-      <c r="B2" s="5"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1071,18 +1121,18 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="6" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1102,31 +1152,31 @@
     </row>
     <row r="5">
       <c r="A5" s="1"/>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="1"/>
@@ -1148,31 +1198,31 @@
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>1.0</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="1"/>
@@ -1194,23 +1244,23 @@
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="12">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="11">
         <v>2.0</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="1"/>
@@ -1232,23 +1282,23 @@
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="12">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="11">
         <v>3.0</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="11" t="s">
         <v>26</v>
       </c>
       <c r="K8" s="1"/>
@@ -1270,15 +1320,15 @@
     </row>
     <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1298,15 +1348,15 @@
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1326,31 +1376,31 @@
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>1.0</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K11" s="1"/>
@@ -1372,23 +1422,23 @@
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="12">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="11">
         <v>2.0</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="11" t="s">
         <v>37</v>
       </c>
       <c r="K12" s="1"/>
@@ -1410,15 +1460,15 @@
     </row>
     <row r="13">
       <c r="A13" s="1"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1438,15 +1488,15 @@
     </row>
     <row r="14">
       <c r="A14" s="1"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1466,15 +1516,15 @@
     </row>
     <row r="15">
       <c r="A15" s="1"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1494,31 +1544,31 @@
     </row>
     <row r="16">
       <c r="A16" s="1"/>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>1.0</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="11" t="s">
         <v>44</v>
       </c>
       <c r="K16" s="1"/>
@@ -1540,23 +1590,23 @@
     </row>
     <row r="17">
       <c r="A17" s="1"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="12">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="11">
         <v>2.0</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="11" t="s">
         <v>47</v>
       </c>
       <c r="K17" s="1"/>
@@ -1578,23 +1628,23 @@
     </row>
     <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="12">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="11">
         <v>3.0</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="11" t="s">
         <v>49</v>
       </c>
       <c r="K18" s="1"/>
@@ -1616,15 +1666,15 @@
     </row>
     <row r="19">
       <c r="A19" s="1"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1644,15 +1694,15 @@
     </row>
     <row r="20">
       <c r="A20" s="1"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1672,31 +1722,31 @@
     </row>
     <row r="21">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="11">
         <v>1.0</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="11" t="s">
         <v>56</v>
       </c>
       <c r="K21" s="1"/>
@@ -1718,23 +1768,23 @@
     </row>
     <row r="22">
       <c r="A22" s="1"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="12">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="11">
         <v>2.0</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="11" t="s">
         <v>60</v>
       </c>
       <c r="K22" s="1"/>
@@ -1756,23 +1806,23 @@
     </row>
     <row r="23">
       <c r="A23" s="1"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="12">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="11">
         <v>3.0</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="11" t="s">
         <v>63</v>
       </c>
       <c r="K23" s="1"/>
@@ -1794,23 +1844,23 @@
     </row>
     <row r="24">
       <c r="A24" s="1"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="12">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="11">
         <v>4.0</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="11" t="s">
         <v>67</v>
       </c>
       <c r="K24" s="1"/>
@@ -1832,15 +1882,15 @@
     </row>
     <row r="25">
       <c r="A25" s="1"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15" t="s">
         <v>68</v>
       </c>
       <c r="K25" s="1"/>
@@ -1862,31 +1912,31 @@
     </row>
     <row r="26">
       <c r="A26" s="1"/>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="11">
         <v>1.0</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="11" t="s">
         <v>76</v>
       </c>
       <c r="K26" s="1"/>
@@ -1908,23 +1958,23 @@
     </row>
     <row r="27">
       <c r="A27" s="1"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="12">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="11">
         <v>2.0</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="11" t="s">
         <v>79</v>
       </c>
       <c r="K27" s="1"/>
@@ -1946,23 +1996,23 @@
     </row>
     <row r="28">
       <c r="A28" s="1"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="12">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="11">
         <v>3.0</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="11" t="s">
         <v>82</v>
       </c>
       <c r="K28" s="1"/>
@@ -1984,15 +2034,15 @@
     </row>
     <row r="29">
       <c r="A29" s="1"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2012,15 +2062,15 @@
     </row>
     <row r="30">
       <c r="A30" s="1"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2040,31 +2090,31 @@
     </row>
     <row r="31">
       <c r="A31" s="1"/>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="11">
         <v>1.0</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="11" t="s">
         <v>90</v>
       </c>
       <c r="K31" s="1"/>
@@ -2086,23 +2136,23 @@
     </row>
     <row r="32">
       <c r="A32" s="1"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="12">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="11">
         <v>2.0</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="11" t="s">
         <v>93</v>
       </c>
       <c r="K32" s="1"/>
@@ -2124,15 +2174,15 @@
     </row>
     <row r="33">
       <c r="A33" s="1"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2152,15 +2202,15 @@
     </row>
     <row r="34">
       <c r="A34" s="1"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2180,15 +2230,15 @@
     </row>
     <row r="35">
       <c r="A35" s="1"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2208,31 +2258,31 @@
     </row>
     <row r="36">
       <c r="A36" s="1"/>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <v>1.0</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="11" t="s">
         <v>101</v>
       </c>
       <c r="K36" s="1"/>
@@ -2254,23 +2304,23 @@
     </row>
     <row r="37">
       <c r="A37" s="1"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="12">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="11">
         <v>2.0</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="11" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="1"/>
@@ -2292,15 +2342,15 @@
     </row>
     <row r="38">
       <c r="A38" s="1"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2320,15 +2370,15 @@
     </row>
     <row r="39">
       <c r="A39" s="1"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2347,16 +2397,16 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40">
-      <c r="A40" s="18"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2375,32 +2425,32 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41">
-      <c r="A41" s="18"/>
-      <c r="B41" s="11" t="s">
+      <c r="A41" s="16"/>
+      <c r="B41" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="11">
         <v>1.0</v>
       </c>
-      <c r="G41" s="12" t="s">
+      <c r="G41" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="I41" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="J41" s="12" t="s">
+      <c r="J41" s="11" t="s">
         <v>111</v>
       </c>
       <c r="K41" s="1"/>
@@ -2421,24 +2471,24 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42">
-      <c r="A42" s="18"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="12">
+      <c r="A42" s="16"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="11">
         <v>2.0</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="J42" s="12" t="s">
+      <c r="J42" s="11" t="s">
         <v>114</v>
       </c>
       <c r="K42" s="1"/>
@@ -2459,16 +2509,16 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43">
-      <c r="A43" s="18"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -2488,15 +2538,15 @@
     </row>
     <row r="44">
       <c r="A44" s="1"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -2515,16 +2565,16 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45">
-      <c r="A45" s="18"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -2543,32 +2593,32 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46">
-      <c r="A46" s="18"/>
-      <c r="B46" s="11" t="s">
+      <c r="A46" s="16"/>
+      <c r="B46" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="11">
         <v>1.0</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="11" t="s">
         <v>122</v>
       </c>
       <c r="K46" s="1"/>
@@ -2589,24 +2639,24 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47">
-      <c r="A47" s="18"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="12">
+      <c r="A47" s="16"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="11">
         <v>2.0</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H47" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="I47" s="12" t="s">
+      <c r="I47" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="11" t="s">
         <v>126</v>
       </c>
       <c r="K47" s="1"/>
@@ -2627,16 +2677,16 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48">
-      <c r="A48" s="18"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="11"/>
+      <c r="I48" s="11"/>
+      <c r="J48" s="11"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -2656,15 +2706,15 @@
     </row>
     <row r="49">
       <c r="A49" s="1"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -2683,16 +2733,16 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50">
-      <c r="A50" s="18"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -2711,32 +2761,32 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51">
-      <c r="A51" s="18"/>
-      <c r="B51" s="11" t="s">
+      <c r="A51" s="16"/>
+      <c r="B51" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="11">
         <v>1.0</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H51" s="12" t="s">
+      <c r="H51" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="I51" s="12" t="s">
+      <c r="I51" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="11" t="s">
         <v>133</v>
       </c>
       <c r="K51" s="1"/>
@@ -2757,24 +2807,24 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52">
-      <c r="A52" s="18"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="12">
+      <c r="A52" s="16"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="11">
         <v>2.0</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="H52" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="I52" s="12" t="s">
+      <c r="I52" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="11" t="s">
         <v>136</v>
       </c>
       <c r="K52" s="1"/>
@@ -2795,24 +2845,24 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53">
-      <c r="A53" s="18"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="12">
+      <c r="A53" s="16"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="11">
         <v>3.0</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="G53" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="H53" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I53" s="12" t="s">
+      <c r="I53" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="J53" s="11" t="s">
         <v>139</v>
       </c>
       <c r="K53" s="1"/>
@@ -2834,15 +2884,15 @@
     </row>
     <row r="54">
       <c r="A54" s="1"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -2861,16 +2911,16 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55">
-      <c r="A55" s="18"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -2889,32 +2939,32 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56">
-      <c r="A56" s="18"/>
-      <c r="B56" s="11" t="s">
+      <c r="A56" s="16"/>
+      <c r="B56" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="11">
         <v>1.0</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="H56" s="12" t="s">
+      <c r="H56" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="I56" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="11" t="s">
         <v>76</v>
       </c>
       <c r="K56" s="1"/>
@@ -2935,24 +2985,24 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57">
-      <c r="A57" s="18"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="12">
+      <c r="A57" s="16"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="11">
         <v>2.0</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="H57" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="I57" s="12" t="s">
+      <c r="I57" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="J57" s="11" t="s">
         <v>79</v>
       </c>
       <c r="K57" s="1"/>
@@ -2973,24 +3023,24 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58">
-      <c r="A58" s="18"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="12">
+      <c r="A58" s="16"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="11">
         <v>3.0</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="11" t="s">
         <v>82</v>
       </c>
       <c r="K58" s="1"/>
@@ -3012,15 +3062,15 @@
     </row>
     <row r="59">
       <c r="A59" s="1"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3039,16 +3089,16 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60">
-      <c r="A60" s="18"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -3067,32 +3117,32 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61">
-      <c r="A61" s="18"/>
-      <c r="B61" s="11" t="s">
+      <c r="A61" s="16"/>
+      <c r="B61" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="11">
         <v>1.0</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="H61" s="12" t="s">
+      <c r="H61" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="I61" s="12" t="s">
+      <c r="I61" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="J61" s="12" t="s">
+      <c r="J61" s="11" t="s">
         <v>154</v>
       </c>
       <c r="K61" s="1"/>
@@ -3113,24 +3163,24 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62">
-      <c r="A62" s="18"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="12">
+      <c r="A62" s="16"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="11">
         <v>2.0</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="I62" s="12" t="s">
+      <c r="I62" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="J62" s="12" t="s">
+      <c r="J62" s="11" t="s">
         <v>157</v>
       </c>
       <c r="K62" s="1"/>
@@ -3151,16 +3201,16 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63">
-      <c r="A63" s="18"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
@@ -3180,15 +3230,15 @@
     </row>
     <row r="64">
       <c r="A64" s="1"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -3207,16 +3257,16 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65">
-      <c r="A65" s="18"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -3235,32 +3285,32 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66">
-      <c r="A66" s="18"/>
-      <c r="B66" s="11" t="s">
+      <c r="A66" s="16"/>
+      <c r="B66" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="11">
         <v>1.0</v>
       </c>
-      <c r="G66" s="12" t="s">
+      <c r="G66" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="H66" s="12" t="s">
+      <c r="H66" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="I66" s="12" t="s">
+      <c r="I66" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="J66" s="12" t="s">
+      <c r="J66" s="11" t="s">
         <v>165</v>
       </c>
       <c r="K66" s="1"/>
@@ -3281,24 +3331,24 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67">
-      <c r="A67" s="18"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="12">
+      <c r="A67" s="16"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="11">
         <v>2.0</v>
       </c>
-      <c r="G67" s="12" t="s">
+      <c r="G67" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="H67" s="12" t="s">
+      <c r="H67" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="I67" s="12" t="s">
+      <c r="I67" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="J67" s="12" t="s">
+      <c r="J67" s="11" t="s">
         <v>165</v>
       </c>
       <c r="K67" s="1"/>
@@ -3319,16 +3369,16 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68">
-      <c r="A68" s="18"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="11"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
@@ -3348,15 +3398,15 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
@@ -3375,16 +3425,16 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="18"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -3402,17 +3452,33 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="18"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+    <row r="71" ht="53.25" customHeight="1">
+      <c r="A71" s="16"/>
+      <c r="B71" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D71" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="F71" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="I71" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="J71" s="11"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -3430,17 +3496,23 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="18"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+    <row r="72" ht="46.5" customHeight="1">
+      <c r="A72" s="16"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="H72" s="11"/>
+      <c r="I72" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="J72" s="11"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
@@ -3458,17 +3530,23 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="18"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+    <row r="73" ht="42.75" customHeight="1">
+      <c r="A73" s="16"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="H73" s="11"/>
+      <c r="I73" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="J73" s="11"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
@@ -3486,17 +3564,16 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" ht="45.75" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="J74" s="11"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
@@ -3516,15 +3593,15 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
@@ -3544,15 +3621,33 @@
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
+      <c r="B76" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F76" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="G76" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H76" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I76" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J76" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
@@ -3572,15 +3667,25 @@
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="G77" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="H77" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I77" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J77" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
@@ -3600,15 +3705,15 @@
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
@@ -3628,15 +3733,15 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="23"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
@@ -3656,15 +3761,15 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
@@ -3684,15 +3789,33 @@
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="B81" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F81" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="G81" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H81" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I81" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J81" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -3712,15 +3835,25 @@
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="H82" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I82" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J82" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
@@ -3740,15 +3873,15 @@
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="23"/>
+      <c r="H83" s="23"/>
+      <c r="I83" s="23"/>
+      <c r="J83" s="23"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
@@ -3768,15 +3901,15 @@
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="23"/>
+      <c r="G84" s="23"/>
+      <c r="H84" s="23"/>
+      <c r="I84" s="23"/>
+      <c r="J84" s="23"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
@@ -3796,15 +3929,15 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
@@ -3824,15 +3957,33 @@
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
+      <c r="B86" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F86" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="G86" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H86" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I86" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J86" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
@@ -3852,15 +4003,25 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="G87" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="H87" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I87" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J87" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
@@ -3880,15 +4041,15 @@
     </row>
     <row r="88" ht="14.25" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="23"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -3908,15 +4069,15 @@
     </row>
     <row r="89" ht="14.25" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
+      <c r="I89" s="23"/>
+      <c r="J89" s="23"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
@@ -3936,15 +4097,15 @@
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="19"/>
+      <c r="E90" s="19"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="19"/>
+      <c r="I90" s="19"/>
+      <c r="J90" s="19"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
@@ -3964,15 +4125,33 @@
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
+      <c r="B91" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E91" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F91" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="G91" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H91" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I91" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J91" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
@@ -3992,15 +4171,25 @@
     </row>
     <row r="92" ht="14.25" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="G92" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="H92" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I92" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J92" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
@@ -4020,15 +4209,15 @@
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="23"/>
+      <c r="J93" s="23"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
@@ -4048,15 +4237,15 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="23"/>
+      <c r="G94" s="23"/>
+      <c r="H94" s="23"/>
+      <c r="I94" s="23"/>
+      <c r="J94" s="23"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
@@ -4076,15 +4265,15 @@
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="19"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="19"/>
+      <c r="F95" s="19"/>
+      <c r="G95" s="19"/>
+      <c r="H95" s="19"/>
+      <c r="I95" s="19"/>
+      <c r="J95" s="19"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
@@ -4104,15 +4293,33 @@
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
+      <c r="B96" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E96" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F96" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="G96" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H96" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I96" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J96" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
@@ -4132,15 +4339,25 @@
     </row>
     <row r="97" ht="14.25" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="1"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="G97" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="H97" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I97" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J97" s="22" t="s">
+        <v>165</v>
+      </c>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
@@ -4160,15 +4377,15 @@
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="19"/>
-      <c r="J98" s="1"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="23"/>
+      <c r="G98" s="23"/>
+      <c r="H98" s="23"/>
+      <c r="I98" s="23"/>
+      <c r="J98" s="23"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
@@ -4188,15 +4405,15 @@
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19"/>
-      <c r="H99" s="19"/>
-      <c r="I99" s="19"/>
-      <c r="J99" s="1"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="23"/>
+      <c r="G99" s="23"/>
+      <c r="H99" s="23"/>
+      <c r="I99" s="23"/>
+      <c r="J99" s="23"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
@@ -4216,14 +4433,14 @@
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
-      <c r="G100" s="19"/>
-      <c r="H100" s="19"/>
-      <c r="I100" s="19"/>
+      <c r="B100" s="24"/>
+      <c r="C100" s="24"/>
+      <c r="D100" s="24"/>
+      <c r="E100" s="24"/>
+      <c r="F100" s="24"/>
+      <c r="G100" s="24"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="24"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -4244,14 +4461,14 @@
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="19"/>
-      <c r="G101" s="19"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="19"/>
+      <c r="B101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="24"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -4272,14 +4489,14 @@
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="20"/>
-      <c r="C102" s="20"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
+      <c r="B102" s="24"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="24"/>
+      <c r="I102" s="24"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -4300,14 +4517,14 @@
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="20"/>
-      <c r="C103" s="20"/>
-      <c r="D103" s="20"/>
-      <c r="E103" s="20"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
+      <c r="B103" s="24"/>
+      <c r="C103" s="24"/>
+      <c r="D103" s="24"/>
+      <c r="E103" s="24"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="24"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -4328,14 +4545,14 @@
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="B104" s="20"/>
-      <c r="C104" s="20"/>
-      <c r="D104" s="20"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="20"/>
-      <c r="G104" s="20"/>
-      <c r="H104" s="20"/>
-      <c r="I104" s="20"/>
+      <c r="B104" s="24"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+      <c r="I104" s="24"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -4356,14 +4573,14 @@
     </row>
     <row r="105" ht="14.25" customHeight="1">
       <c r="A105" s="1"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19"/>
-      <c r="F105" s="19"/>
-      <c r="G105" s="20"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="20"/>
+      <c r="B105" s="24"/>
+      <c r="C105" s="24"/>
+      <c r="D105" s="24"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="24"/>
+      <c r="G105" s="24"/>
+      <c r="H105" s="24"/>
+      <c r="I105" s="24"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -4384,14 +4601,14 @@
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="1"/>
-      <c r="B106" s="19"/>
-      <c r="C106" s="19"/>
-      <c r="D106" s="19"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="20"/>
-      <c r="H106" s="19"/>
-      <c r="I106" s="20"/>
+      <c r="B106" s="24"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+      <c r="I106" s="24"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -4412,14 +4629,14 @@
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-      <c r="D107" s="19"/>
-      <c r="E107" s="19"/>
-      <c r="F107" s="19"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
-      <c r="I107" s="20"/>
+      <c r="B107" s="24"/>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
+      <c r="I107" s="24"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -4440,14 +4657,14 @@
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c r="A108" s="1"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-      <c r="D108" s="19"/>
-      <c r="E108" s="19"/>
-      <c r="F108" s="19"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
+      <c r="B108" s="24"/>
+      <c r="C108" s="24"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="24"/>
+      <c r="H108" s="24"/>
+      <c r="I108" s="24"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -4468,14 +4685,14 @@
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c r="A109" s="1"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-      <c r="D109" s="19"/>
-      <c r="E109" s="19"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
+      <c r="B109" s="24"/>
+      <c r="C109" s="24"/>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="24"/>
+      <c r="H109" s="24"/>
+      <c r="I109" s="24"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -4496,14 +4713,14 @@
     </row>
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="1"/>
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-      <c r="D110" s="19"/>
-      <c r="E110" s="19"/>
-      <c r="F110" s="19"/>
-      <c r="G110" s="20"/>
-      <c r="H110" s="20"/>
-      <c r="I110" s="20"/>
+      <c r="B110" s="24"/>
+      <c r="C110" s="24"/>
+      <c r="D110" s="24"/>
+      <c r="E110" s="24"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="24"/>
+      <c r="H110" s="24"/>
+      <c r="I110" s="24"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -4524,14 +4741,14 @@
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="1"/>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="19"/>
-      <c r="E111" s="19"/>
-      <c r="F111" s="19"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
-      <c r="I111" s="20"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+      <c r="I111" s="24"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -4552,14 +4769,14 @@
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="19"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
-      <c r="I112" s="20"/>
+      <c r="B112" s="24"/>
+      <c r="C112" s="24"/>
+      <c r="D112" s="24"/>
+      <c r="E112" s="24"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+      <c r="H112" s="24"/>
+      <c r="I112" s="24"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
@@ -4580,14 +4797,14 @@
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="1"/>
-      <c r="B113" s="20"/>
-      <c r="C113" s="20"/>
-      <c r="D113" s="20"/>
-      <c r="E113" s="20"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
+      <c r="B113" s="24"/>
+      <c r="C113" s="24"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="24"/>
+      <c r="I113" s="24"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -4608,14 +4825,14 @@
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="1"/>
-      <c r="B114" s="20"/>
-      <c r="C114" s="20"/>
-      <c r="D114" s="20"/>
-      <c r="E114" s="20"/>
-      <c r="F114" s="20"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="20"/>
-      <c r="I114" s="20"/>
+      <c r="B114" s="24"/>
+      <c r="C114" s="24"/>
+      <c r="D114" s="24"/>
+      <c r="E114" s="24"/>
+      <c r="F114" s="24"/>
+      <c r="G114" s="24"/>
+      <c r="H114" s="24"/>
+      <c r="I114" s="24"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
@@ -4636,14 +4853,14 @@
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="1"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="20"/>
-      <c r="D115" s="20"/>
-      <c r="E115" s="20"/>
-      <c r="F115" s="20"/>
-      <c r="G115" s="20"/>
-      <c r="H115" s="20"/>
-      <c r="I115" s="20"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
@@ -4664,14 +4881,14 @@
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="1"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="20"/>
-      <c r="D116" s="20"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="20"/>
-      <c r="G116" s="20"/>
-      <c r="H116" s="20"/>
-      <c r="I116" s="20"/>
+      <c r="B116" s="24"/>
+      <c r="C116" s="24"/>
+      <c r="D116" s="24"/>
+      <c r="E116" s="24"/>
+      <c r="F116" s="24"/>
+      <c r="G116" s="24"/>
+      <c r="H116" s="24"/>
+      <c r="I116" s="24"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
@@ -4692,14 +4909,14 @@
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="20"/>
-      <c r="C117" s="20"/>
-      <c r="D117" s="20"/>
-      <c r="E117" s="20"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
+      <c r="B117" s="24"/>
+      <c r="C117" s="24"/>
+      <c r="D117" s="24"/>
+      <c r="E117" s="24"/>
+      <c r="F117" s="24"/>
+      <c r="G117" s="24"/>
+      <c r="H117" s="24"/>
+      <c r="I117" s="24"/>
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
       <c r="L117" s="1"/>
@@ -4720,14 +4937,14 @@
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="1"/>
-      <c r="B118" s="20"/>
-      <c r="C118" s="20"/>
-      <c r="D118" s="20"/>
-      <c r="E118" s="20"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="20"/>
-      <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
+      <c r="B118" s="24"/>
+      <c r="C118" s="24"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="24"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
@@ -4748,14 +4965,14 @@
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="20"/>
-      <c r="C119" s="20"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="20"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
-      <c r="I119" s="20"/>
+      <c r="B119" s="24"/>
+      <c r="C119" s="24"/>
+      <c r="D119" s="24"/>
+      <c r="E119" s="24"/>
+      <c r="F119" s="24"/>
+      <c r="G119" s="24"/>
+      <c r="H119" s="24"/>
+      <c r="I119" s="24"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
@@ -4776,14 +4993,14 @@
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="1"/>
-      <c r="B120" s="20"/>
-      <c r="C120" s="20"/>
-      <c r="D120" s="20"/>
-      <c r="E120" s="20"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
-      <c r="I120" s="20"/>
+      <c r="B120" s="24"/>
+      <c r="C120" s="24"/>
+      <c r="D120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="24"/>
+      <c r="I120" s="24"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
@@ -4804,14 +5021,14 @@
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="20"/>
-      <c r="C121" s="20"/>
-      <c r="D121" s="20"/>
-      <c r="E121" s="20"/>
-      <c r="F121" s="20"/>
-      <c r="G121" s="20"/>
-      <c r="H121" s="20"/>
-      <c r="I121" s="20"/>
+      <c r="B121" s="24"/>
+      <c r="C121" s="24"/>
+      <c r="D121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
@@ -4832,14 +5049,14 @@
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="20"/>
-      <c r="C122" s="20"/>
-      <c r="D122" s="20"/>
-      <c r="E122" s="20"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
+      <c r="B122" s="24"/>
+      <c r="C122" s="24"/>
+      <c r="D122" s="24"/>
+      <c r="E122" s="24"/>
+      <c r="F122" s="24"/>
+      <c r="G122" s="24"/>
+      <c r="H122" s="24"/>
+      <c r="I122" s="24"/>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
@@ -4860,14 +5077,14 @@
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="1"/>
-      <c r="B123" s="20"/>
-      <c r="C123" s="20"/>
-      <c r="D123" s="20"/>
-      <c r="E123" s="20"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
-      <c r="I123" s="20"/>
+      <c r="B123" s="24"/>
+      <c r="C123" s="24"/>
+      <c r="D123" s="24"/>
+      <c r="E123" s="24"/>
+      <c r="F123" s="24"/>
+      <c r="G123" s="24"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
@@ -4888,14 +5105,14 @@
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="1"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="20"/>
-      <c r="D124" s="20"/>
-      <c r="E124" s="20"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
-      <c r="I124" s="20"/>
+      <c r="B124" s="24"/>
+      <c r="C124" s="24"/>
+      <c r="D124" s="24"/>
+      <c r="E124" s="24"/>
+      <c r="F124" s="24"/>
+      <c r="G124" s="24"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
@@ -4916,14 +5133,14 @@
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="20"/>
-      <c r="C125" s="20"/>
-      <c r="D125" s="20"/>
-      <c r="E125" s="20"/>
-      <c r="F125" s="20"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
-      <c r="I125" s="20"/>
+      <c r="B125" s="24"/>
+      <c r="C125" s="24"/>
+      <c r="D125" s="24"/>
+      <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
@@ -4944,14 +5161,14 @@
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="20"/>
-      <c r="C126" s="20"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="20"/>
-      <c r="I126" s="20"/>
+      <c r="B126" s="24"/>
+      <c r="C126" s="24"/>
+      <c r="D126" s="24"/>
+      <c r="E126" s="24"/>
+      <c r="F126" s="24"/>
+      <c r="G126" s="24"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -4972,14 +5189,14 @@
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="20"/>
-      <c r="C127" s="20"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="20"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="20"/>
-      <c r="I127" s="20"/>
+      <c r="B127" s="24"/>
+      <c r="C127" s="24"/>
+      <c r="D127" s="24"/>
+      <c r="E127" s="24"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
@@ -5000,14 +5217,14 @@
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="1"/>
-      <c r="B128" s="20"/>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="20"/>
-      <c r="I128" s="20"/>
+      <c r="B128" s="24"/>
+      <c r="C128" s="24"/>
+      <c r="D128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
@@ -5028,14 +5245,14 @@
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="1"/>
-      <c r="B129" s="20"/>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
-      <c r="I129" s="20"/>
+      <c r="B129" s="24"/>
+      <c r="C129" s="24"/>
+      <c r="D129" s="24"/>
+      <c r="E129" s="24"/>
+      <c r="F129" s="24"/>
+      <c r="G129" s="24"/>
+      <c r="H129" s="24"/>
+      <c r="I129" s="24"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
@@ -28911,7 +29128,7 @@
       <c r="Z981" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="79">
     <mergeCell ref="B36:B39"/>
     <mergeCell ref="B41:B44"/>
     <mergeCell ref="C41:C44"/>
@@ -28919,10 +29136,6 @@
     <mergeCell ref="E41:E44"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="C46:C49"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="E66:E69"/>
     <mergeCell ref="B51:B54"/>
     <mergeCell ref="C51:C54"/>
     <mergeCell ref="D51:D54"/>
@@ -28930,6 +29143,34 @@
     <mergeCell ref="C56:C59"/>
     <mergeCell ref="D56:D59"/>
     <mergeCell ref="E56:E59"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="D81:D84"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="E76:E79"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="E96:E99"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="C91:C94"/>
+    <mergeCell ref="D91:D94"/>
+    <mergeCell ref="E91:E94"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:J4"/>

--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.2 Épicas e Historias de Usuario/Historias Usuario con instructivo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.2 Épicas e Historias de Usuario/Historias Usuario con instructivo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="259">
   <si>
     <t>Desarrollo ágil: Historias de usuario y criterios de aceptación</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Resultado / Comportamiento esperado</t>
   </si>
   <si>
-    <t>EP-01/HU-01</t>
+    <t>EP-02/HU-01</t>
   </si>
   <si>
     <t>Como nuevo usuario</t>
@@ -99,7 +99,7 @@
     <t>El sistema mostrará un mensaje erróneo comunicando que la cuenta ya se encuentra registrada</t>
   </si>
   <si>
-    <t>EP-02/HU-02</t>
+    <t>EP-01/HU-02</t>
   </si>
   <si>
     <t>Como usuario registrado</t>
@@ -111,7 +111,7 @@
     <t>para acceder a las funciones de la aplicación</t>
   </si>
   <si>
-    <t>Inicio sección exitoso</t>
+    <t>Inicio sesión exitoso</t>
   </si>
   <si>
     <t>Al iniciar sesion puede lograrse sin inconvenientes</t>
@@ -120,10 +120,10 @@
     <t>Login</t>
   </si>
   <si>
-    <t>El sistema continuará con el ingreso por PIN</t>
+    <t>El sistema continuará con el ingreso por PIN, dependiendo del PIN reconocerá usuario principal o apadrinado</t>
   </si>
   <si>
-    <t>Inicio sección ERROR</t>
+    <t>Inicio sesión ERROR</t>
   </si>
   <si>
     <t>Al iniciar sesion puede NO lograrse debido a errores de credenciales</t>
@@ -295,10 +295,10 @@
     <t>Alerta sin conexión a Internet</t>
   </si>
   <si>
-    <t>El usuario presiona el botón SOS en una zona donde el dispositivo móvil no tiene cobertura de datos o Wi-Fi.</t>
+    <t>El usuario presiona el botón SOS en una zona donde el dispositivo móvil no tiene Wi-Fi.</t>
   </si>
   <si>
-    <t>El sistema intentará enviar la alerta a través de un mensaje SMS de respaldo (fallback) a los números telefónicos registrados de los contactos.</t>
+    <t>El sistema intentará enviar la alerta al backend con su ubicación y mensaje personalizado, con esto, el backend envia notificaciones push a los contactos de emergencia del usuario</t>
   </si>
   <si>
     <t>EP-05/HU-07</t>
@@ -379,25 +379,31 @@
     <t>Creación y vinculación exitosa</t>
   </si>
   <si>
-    <t>El usuario tutor se encuentra logueado y puede añadir a un usuario externo a base de un pago</t>
+    <t>El usuario principal se encuentra logueado, tiene cupos y puede añadir a un usuario apadrinado a base del pago de un cupo</t>
   </si>
   <si>
-    <t>Pago exitoso</t>
+    <t>Vincular usuario apadrinado</t>
   </si>
   <si>
-    <t>El sistema muestra un mensaje de compra exitosa y deriva a la personalización de usuarios.</t>
+    <t xml:space="preserve">El sistema solicita el PIN del usuario principal y crea la cuenta apadrinada vinculada a la principal, con sus datos aislados para su edición. Se descuenta un cupo de usuarios apadrinados </t>
   </si>
   <si>
-    <t>Compra fallida</t>
+    <t>Sin cupos disponibles</t>
   </si>
   <si>
-    <t>El usuario tutor no pudo realizar el pago debido a fallas con la tarjeta</t>
+    <t>El usuario principal intenta comprar un cupo habiendo ya utilizado todos sus cupos de usuarios apadrinados (maximo 5)</t>
   </si>
   <si>
-    <t>Pago ERROR</t>
+    <t>El sistema no procede con el pago del cupo y muestra el mensaje "Cupo maximo de usuarios apadrinados alcanzado, no es posible la compra ni la vinculación de otro usuario. Por favor modifique y/o elimine sus usuarios apadrinados ya existentes"</t>
   </si>
   <si>
-    <t>El sistema no procede con el pago de la cuenta nueva y vuelve a darle la opción de volver a intentar.</t>
+    <t>PIN incorrecto a la creación del usuario apadrinado</t>
+  </si>
+  <si>
+    <t>El usuario principal al crear/editar un usuario apadrinado ingresa incorrectamente su PIN</t>
+  </si>
+  <si>
+    <t>El sistema rechaza la vinculación y aplica la regla de intentos</t>
   </si>
   <si>
     <t>EP-07/HU-10</t>
@@ -424,7 +430,7 @@
     <t>Validación de formato incorrecto</t>
   </si>
   <si>
-    <t>El usuario tuto intentó ingresar un pin sin respetar el formato indicado</t>
+    <t>El usuario tutor intentó ingresar un pin sin respetar el formato indicado</t>
   </si>
   <si>
     <t>El sistema solicita reintentar el ingreso del pin a guardar.</t>
@@ -437,6 +443,21 @@
   </si>
   <si>
     <t>El sistema entrega un mensaje que menciona que este usuario no podrá cambiar el PIN a menos de que la cuenta tutor desee.</t>
+  </si>
+  <si>
+    <t>PIN bloqueado por intentos</t>
+  </si>
+  <si>
+    <t>El usuario tutor ingresa tres veces un PIN incorrecto</t>
+  </si>
+  <si>
+    <t>Validación PIN</t>
+  </si>
+  <si>
+    <t>El sistema bloquea la acción por 5 minutos, el bloqueo se aplica dentro del servidor, en todos los dispositivos de la cuenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>EP-08/HU-11</t>
@@ -459,6 +480,18 @@
   </si>
   <si>
     <t>El usuario se encuentra personalizando el texto de la alerta de antecedente médico y lo deja vacío.</t>
+  </si>
+  <si>
+    <t>Datos medicos quedan cifrados</t>
+  </si>
+  <si>
+    <t>Se tratan de ver los datos medicos por alguien que no se el usuario o sus contactos de emergencia.</t>
+  </si>
+  <si>
+    <t>Cifrado de datos medicos</t>
+  </si>
+  <si>
+    <t>El sistema hace un cifrado de los datos o los oculta ante personas no autorizadas.</t>
   </si>
   <si>
     <t>EP-08/HU-12</t>
@@ -491,7 +524,7 @@
     <t>El sistema no encuentra información relevante increada del usuario</t>
   </si>
   <si>
-    <t>El sistema debe poder enviar una alerta de emergencia con información importante, si no llegase haber información relevante el usuario no podrá enviar un mensaje de emergencia</t>
+    <t>El sistema debe poder enviar una alerta de emergencia con información importante, si no llegase haber información relevante, se enviara un mensaje generico de emergencia.</t>
   </si>
   <si>
     <t>EP-09/HU-13</t>
@@ -507,19 +540,262 @@
 </t>
   </si>
   <si>
-    <t>Generar un CRUD de los usuarios y sus usuarios apadrinados</t>
+    <t>Listar y filtrar cuentas</t>
   </si>
   <si>
-    <t>Se debe poder modificar, eliminar, agregar y buscar datos relevantes para caso de inconvenientes técnicos</t>
+    <t>El administrador está autenticado con el rol "Administador" en el panel</t>
   </si>
   <si>
-    <t>CRUD</t>
+    <t>Buscar cuentas</t>
   </si>
   <si>
-    <t>El sistema debe entregar la información actualizada a tiempo real</t>
+    <t xml:space="preserve">El sistema lista las cuentas principales y apadrinadas con su correo, estado, nivel de acceso, acciones y alertas, sin mostrar información medica </t>
   </si>
   <si>
-    <t xml:space="preserve">Generar un CRUD de los datos de compra de los usuarios </t>
+    <t>Cambiar estado o rol de una cuenta</t>
+  </si>
+  <si>
+    <t>El administrador bloquea, reactiva o cambia el rol (dependiendo del caso) de una cuenta distinta de la suya</t>
+  </si>
+  <si>
+    <t>Gestionar cuenta</t>
+  </si>
+  <si>
+    <t>El sistema aplica el cambio, lo registra en la bitácora. Si se intenta cambiar el rol del mismo administrador se rechaza el cambio</t>
+  </si>
+  <si>
+    <t>Consulta de compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El administrador consulta las compras realizadas en el sistema o de un usuario </t>
+  </si>
+  <si>
+    <t>Consultar compras</t>
+  </si>
+  <si>
+    <t>El sistema muestra las ventas solo en modo lectura, estas no pueden ser ni modificadas ni eliminadas</t>
+  </si>
+  <si>
+    <t>EP-05/HU-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usuario que activó una alerta (o usuario apadrinado) </t>
+  </si>
+  <si>
+    <t>quiero finalizar una alerta generada</t>
+  </si>
+  <si>
+    <t>para que mis contactos sepan que la situación terminó y se revoque el acceso a mi información medica</t>
+  </si>
+  <si>
+    <t>Finalizar emergencia</t>
+  </si>
+  <si>
+    <t>El usuario tiene una alerta ACTIVA y ya puede finalizar la misma por su propia cuenta</t>
+  </si>
+  <si>
+    <t>El sistema pide una confirmación, cambia el estado a FINALIZADA y revoca el acceso medico e informa a los contactos que la situación terminó</t>
+  </si>
+  <si>
+    <t>Expiración automatica</t>
+  </si>
+  <si>
+    <t>Una alerta sigue ACTIVA pasadas 24 horas desde su activación</t>
+  </si>
+  <si>
+    <t>Tarea automatica</t>
+  </si>
+  <si>
+    <t>El sistema cambia el estado a EXPIRADA y revoca el enlace a información medica</t>
+  </si>
+  <si>
+    <t>Emergencia ya cerrada</t>
+  </si>
+  <si>
+    <t>El usuario intenta cerrar una alerta ya finalizada</t>
+  </si>
+  <si>
+    <t>Alerta finalizada</t>
+  </si>
+  <si>
+    <t>El sistema rechaza la acción, entregando el mensaje "La emergencia ya fue cerrada", sin cambiar el estado de la misma</t>
+  </si>
+  <si>
+    <t>EP-02/HU-15</t>
+  </si>
+  <si>
+    <t>quiero modificar mis credenciales de inicio de sesión (contraseña)</t>
+  </si>
+  <si>
+    <t>para mantener mis credenciales de acceso y perfil actualizadas</t>
+  </si>
+  <si>
+    <t>Cambio de contraseña exitoso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario autenticado solicita un cambio de contraseña mediante recuperación por correo electronico e ingresa contraseña con el formato adecuado </t>
+  </si>
+  <si>
+    <t>Actualizar credenciales</t>
+  </si>
+  <si>
+    <t>El sistema guarda el hash de la contraseña y confirma el cambio</t>
+  </si>
+  <si>
+    <t>Cambio de contraseña erroneo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario autenticado solicita un cambio de contraseña mediante recuperación por correo electronico e ingresa contraseña con el formato incorrecto </t>
+  </si>
+  <si>
+    <t>El sistema rechaza el cambio con el mensaje "No fue posible cambiar la contraseña. Verifique el formato ingresado"</t>
+  </si>
+  <si>
+    <t>EP-07/HU-16</t>
+  </si>
+  <si>
+    <t>Como usuario principal</t>
+  </si>
+  <si>
+    <t>quiero comprar un plan o cupos para usuarios apadrinados desde la aplicación web</t>
+  </si>
+  <si>
+    <t>para acceder a las funciones principales del sistema y/o ampliar la protección a mis dependientes</t>
+  </si>
+  <si>
+    <t>Pago exitoso de cupos</t>
+  </si>
+  <si>
+    <t>El usuario se encuentra logeado, tiene plan, tiene cupos disponibles para añadir un usuario apadrinado, y añade un cupo mediante un pago por la pasarela de pagos</t>
+  </si>
+  <si>
+    <t>Pago exitoso</t>
+  </si>
+  <si>
+    <t>El sistema muestra el mensaje "La compra fue realizada exitosamente" y registra el cupo en la cuenta del usuario principal</t>
+  </si>
+  <si>
+    <t>Pago exitoso de plan</t>
+  </si>
+  <si>
+    <t>El usuario se encuentra logeado, no tiene plan y adquiere uno mediante un pago por la pasarela de pagos</t>
+  </si>
+  <si>
+    <t>El sistema muestra el mensaje "La compra fue realizada exitosamente" y convierte al usuario en usuario principal, habilitando las funciones principales del sistema de alertas</t>
+  </si>
+  <si>
+    <t>Pago rechazado</t>
+  </si>
+  <si>
+    <t>El usuario no pudo realizar el pago debido a fallos en ingreso de datos</t>
+  </si>
+  <si>
+    <t>Pago erroneo</t>
+  </si>
+  <si>
+    <t>El sistema no procede con el pago y muestra el mensaje "El formato de datos de pagos ingresado es erroneo, por favor intenta nuevamente"</t>
+  </si>
+  <si>
+    <t>El usuario no pudo realizar el pago debido a fallos de la pasarela de pago</t>
+  </si>
+  <si>
+    <t>El sistema no procede con el pago y muestra el mensaje "La pasarela de pagos está inhabilitada temporalmente, por favor intente nuevamente mas tarde"</t>
+  </si>
+  <si>
+    <t>EP-04/HU-17</t>
+  </si>
+  <si>
+    <t>Como usuario principal/apadrinado</t>
+  </si>
+  <si>
+    <t>quiero ver los números oficiales de emergencia con acceso directo a llamada</t>
+  </si>
+  <si>
+    <t>para contactar rapidamente a los servicios publicos de emergencia al momento de una alerta</t>
+  </si>
+  <si>
+    <t>Llamar a un número oficial</t>
+  </si>
+  <si>
+    <t>El usuario, al generar una alerta en la aplicación movil, puede llamar directamente a los servicios de emergencia</t>
+  </si>
+  <si>
+    <t>Números oficiales</t>
+  </si>
+  <si>
+    <t>El sistema muestra los numeros de emergencia (131, 132, 133) con un acceso directo de llamada directa, nunca realizando llamados automaticos a dichos servicios</t>
+  </si>
+  <si>
+    <t>EP-09/HU-18</t>
+  </si>
+  <si>
+    <t>Como usuario o visitante</t>
+  </si>
+  <si>
+    <t>quiero enviar una solicitud de soporte</t>
+  </si>
+  <si>
+    <t>para recibir ayuda ante problemas con la aplicación</t>
+  </si>
+  <si>
+    <t>Solicitud valida (usuario registrado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario completa el formulario de solicitud con categoría y descripción, esta incluye su nombre de usuario y correo </t>
+  </si>
+  <si>
+    <t>Enviar solicitud</t>
+  </si>
+  <si>
+    <t>El sistema crea el ticket, muestra el identificador de la solicitud y el estado inicial de la misma</t>
+  </si>
+  <si>
+    <t>Solicitud valida (usuario visitante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario completa el formulario de solicitud con categoría y descripción, redactando el mismo su nombre y correo electronico para una posterior respuesta </t>
+  </si>
+  <si>
+    <t>El sistema crea el ticket, muestra el identificador de la solicitud y el estado inicial de la misma mediante correo electronico</t>
+  </si>
+  <si>
+    <t>Formulario incompleto</t>
+  </si>
+  <si>
+    <t>El usuario, al redactar el formulario,omite un campo obligatorio o ingresa un correo invalido</t>
+  </si>
+  <si>
+    <t>El sistema no envia la solicitud y muestra el mensaje "El formulario está incorrecto, por favor verifique los campos obligatorios y/o el correo ingresado"</t>
+  </si>
+  <si>
+    <t>EP-09/HU-19</t>
+  </si>
+  <si>
+    <t>quiero generar un informe de la actividad de mi cuenta y los usuarios apadrinados</t>
+  </si>
+  <si>
+    <t>para revisar el historial de alertas y acciones</t>
+  </si>
+  <si>
+    <t>Informe con datos</t>
+  </si>
+  <si>
+    <t>El usuario principal solicita un informe de actividades, cuando tanto alertas como acciones dentro de su cuenta o los usuarios apadrinados fueron realizadas</t>
+  </si>
+  <si>
+    <t>Generar informe</t>
+  </si>
+  <si>
+    <t>El sistema genera un PDF solo con la actividad de su cuenta y de sus apadrinados</t>
+  </si>
+  <si>
+    <t>Sin datos de historial</t>
+  </si>
+  <si>
+    <t>El usuario principal solicita un informe de actividades, cuando tanto alertas como acciones NO se han realizado dentro de su cuenta o los usuarios apadrinados</t>
+  </si>
+  <si>
+    <t>El sistema informa "No existen registros para realizar un informe correctamente" y evita la descarga del mismo</t>
   </si>
 </sst>
 </file>
@@ -594,7 +870,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left/>
@@ -608,11 +884,6 @@
       <bottom/>
     </border>
     <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <right/>
       <top/>
       <bottom/>
     </border>
@@ -704,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -715,43 +986,53 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="7" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -993,7 +1274,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
+      <c r="I1" s="3"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1014,7 +1295,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1"/>
-      <c r="B2" s="5"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1071,18 +1352,18 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="6" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1102,31 +1383,31 @@
     </row>
     <row r="5">
       <c r="A5" s="1"/>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="1"/>
@@ -1148,31 +1429,31 @@
     </row>
     <row r="6">
       <c r="A6" s="1"/>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>1.0</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="1"/>
@@ -1194,23 +1475,23 @@
     </row>
     <row r="7">
       <c r="A7" s="1"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="12">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="11">
         <v>2.0</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="1"/>
@@ -1232,23 +1513,23 @@
     </row>
     <row r="8">
       <c r="A8" s="1"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="12">
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="11">
         <v>3.0</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="11" t="s">
         <v>26</v>
       </c>
       <c r="K8" s="1"/>
@@ -1270,15 +1551,15 @@
     </row>
     <row r="9">
       <c r="A9" s="1"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1298,15 +1579,15 @@
     </row>
     <row r="10">
       <c r="A10" s="1"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -1326,31 +1607,31 @@
     </row>
     <row r="11">
       <c r="A11" s="1"/>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>1.0</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K11" s="1"/>
@@ -1372,23 +1653,23 @@
     </row>
     <row r="12">
       <c r="A12" s="1"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="12">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="11">
         <v>2.0</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="11" t="s">
         <v>37</v>
       </c>
       <c r="K12" s="1"/>
@@ -1410,15 +1691,15 @@
     </row>
     <row r="13">
       <c r="A13" s="1"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -1438,15 +1719,15 @@
     </row>
     <row r="14">
       <c r="A14" s="1"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -1466,15 +1747,15 @@
     </row>
     <row r="15">
       <c r="A15" s="1"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -1494,31 +1775,31 @@
     </row>
     <row r="16">
       <c r="A16" s="1"/>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>1.0</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="11" t="s">
         <v>44</v>
       </c>
       <c r="K16" s="1"/>
@@ -1540,23 +1821,23 @@
     </row>
     <row r="17">
       <c r="A17" s="1"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="12">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="11">
         <v>2.0</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="11" t="s">
         <v>47</v>
       </c>
       <c r="K17" s="1"/>
@@ -1578,23 +1859,23 @@
     </row>
     <row r="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="12">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="11">
         <v>3.0</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="I18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="11" t="s">
         <v>49</v>
       </c>
       <c r="K18" s="1"/>
@@ -1616,15 +1897,15 @@
     </row>
     <row r="19">
       <c r="A19" s="1"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -1644,15 +1925,15 @@
     </row>
     <row r="20">
       <c r="A20" s="1"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -1672,31 +1953,31 @@
     </row>
     <row r="21">
       <c r="A21" s="1"/>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="11">
         <v>1.0</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="11" t="s">
         <v>56</v>
       </c>
       <c r="K21" s="1"/>
@@ -1718,23 +1999,23 @@
     </row>
     <row r="22">
       <c r="A22" s="1"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="12">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="11">
         <v>2.0</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="11" t="s">
         <v>60</v>
       </c>
       <c r="K22" s="1"/>
@@ -1756,23 +2037,23 @@
     </row>
     <row r="23">
       <c r="A23" s="1"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="12">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="11">
         <v>3.0</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="11" t="s">
         <v>63</v>
       </c>
       <c r="K23" s="1"/>
@@ -1794,23 +2075,23 @@
     </row>
     <row r="24">
       <c r="A24" s="1"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="12">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="11">
         <v>4.0</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="11" t="s">
         <v>67</v>
       </c>
       <c r="K24" s="1"/>
@@ -1832,15 +2113,15 @@
     </row>
     <row r="25">
       <c r="A25" s="1"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15" t="s">
         <v>68</v>
       </c>
       <c r="K25" s="1"/>
@@ -1862,31 +2143,31 @@
     </row>
     <row r="26">
       <c r="A26" s="1"/>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="11">
         <v>1.0</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="I26" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="11" t="s">
         <v>76</v>
       </c>
       <c r="K26" s="1"/>
@@ -1908,23 +2189,23 @@
     </row>
     <row r="27">
       <c r="A27" s="1"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="12">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="11">
         <v>2.0</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="11" t="s">
         <v>79</v>
       </c>
       <c r="K27" s="1"/>
@@ -1946,23 +2227,23 @@
     </row>
     <row r="28">
       <c r="A28" s="1"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="12">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="11">
         <v>3.0</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="11" t="s">
         <v>82</v>
       </c>
       <c r="K28" s="1"/>
@@ -1984,15 +2265,15 @@
     </row>
     <row r="29">
       <c r="A29" s="1"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2012,15 +2293,15 @@
     </row>
     <row r="30">
       <c r="A30" s="1"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -2040,31 +2321,31 @@
     </row>
     <row r="31">
       <c r="A31" s="1"/>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="11">
         <v>1.0</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="11" t="s">
         <v>90</v>
       </c>
       <c r="K31" s="1"/>
@@ -2086,23 +2367,23 @@
     </row>
     <row r="32">
       <c r="A32" s="1"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="12">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="11">
         <v>2.0</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="11" t="s">
         <v>93</v>
       </c>
       <c r="K32" s="1"/>
@@ -2124,15 +2405,15 @@
     </row>
     <row r="33">
       <c r="A33" s="1"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2152,15 +2433,15 @@
     </row>
     <row r="34">
       <c r="A34" s="1"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -2180,15 +2461,15 @@
     </row>
     <row r="35">
       <c r="A35" s="1"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -2208,31 +2489,31 @@
     </row>
     <row r="36">
       <c r="A36" s="1"/>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <v>1.0</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="H36" s="12" t="s">
+      <c r="H36" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="11" t="s">
         <v>101</v>
       </c>
       <c r="K36" s="1"/>
@@ -2254,23 +2535,23 @@
     </row>
     <row r="37">
       <c r="A37" s="1"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="12">
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="11">
         <v>2.0</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="11" t="s">
         <v>104</v>
       </c>
       <c r="K37" s="1"/>
@@ -2292,15 +2573,15 @@
     </row>
     <row r="38">
       <c r="A38" s="1"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -2320,15 +2601,15 @@
     </row>
     <row r="39">
       <c r="A39" s="1"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -2347,16 +2628,16 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40">
-      <c r="A40" s="18"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -2375,32 +2656,32 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41">
-      <c r="A41" s="18"/>
-      <c r="B41" s="11" t="s">
+      <c r="A41" s="16"/>
+      <c r="B41" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="11">
         <v>1.0</v>
       </c>
-      <c r="G41" s="12" t="s">
+      <c r="G41" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="I41" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="J41" s="12" t="s">
+      <c r="J41" s="11" t="s">
         <v>111</v>
       </c>
       <c r="K41" s="1"/>
@@ -2421,24 +2702,24 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42">
-      <c r="A42" s="18"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="12">
+      <c r="A42" s="16"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="11">
         <v>2.0</v>
       </c>
-      <c r="G42" s="12" t="s">
+      <c r="G42" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="H42" s="12" t="s">
+      <c r="H42" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I42" s="12" t="s">
+      <c r="I42" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="J42" s="12" t="s">
+      <c r="J42" s="11" t="s">
         <v>114</v>
       </c>
       <c r="K42" s="1"/>
@@ -2459,16 +2740,16 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43">
-      <c r="A43" s="18"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
+      <c r="A43" s="16"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -2488,15 +2769,15 @@
     </row>
     <row r="44">
       <c r="A44" s="1"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -2515,16 +2796,16 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45">
-      <c r="A45" s="18"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -2543,32 +2824,32 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46">
-      <c r="A46" s="18"/>
-      <c r="B46" s="11" t="s">
+      <c r="A46" s="16"/>
+      <c r="B46" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="11">
         <v>1.0</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="I46" s="12" t="s">
+      <c r="I46" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="11" t="s">
         <v>122</v>
       </c>
       <c r="K46" s="1"/>
@@ -2589,25 +2870,25 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47">
-      <c r="A47" s="18"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="12">
+      <c r="A47" s="16"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="11">
         <v>2.0</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H47" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="I47" s="12" t="s">
+      <c r="I47" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J47" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>126</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2627,16 +2908,26 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48">
-      <c r="A48" s="18"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -2656,15 +2947,15 @@
     </row>
     <row r="49">
       <c r="A49" s="1"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -2683,16 +2974,16 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50">
-      <c r="A50" s="18"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17"/>
-      <c r="I50" s="17"/>
-      <c r="J50" s="17"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -2711,33 +3002,33 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51">
-      <c r="A51" s="18"/>
-      <c r="B51" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C51" s="11" t="s">
+      <c r="A51" s="16"/>
+      <c r="B51" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F51" s="12">
+      <c r="D51" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F51" s="11">
         <v>1.0</v>
       </c>
-      <c r="G51" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="H51" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="I51" s="12" t="s">
+      <c r="G51" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="H51" s="11" t="s">
         <v>133</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2757,25 +3048,25 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52">
-      <c r="A52" s="18"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="12">
+      <c r="A52" s="16"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="11">
         <v>2.0</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I52" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="H52" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>136</v>
+      <c r="J52" s="11" t="s">
+        <v>138</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2795,25 +3086,25 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53">
-      <c r="A53" s="18"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="12">
+      <c r="A53" s="16"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="11">
         <v>3.0</v>
       </c>
-      <c r="G53" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="H53" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="J53" s="12" t="s">
+      <c r="G53" s="11" t="s">
         <v>139</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>141</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2832,18 +3123,30 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" ht="45.0" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="1"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="G54" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="H54" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I54" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="J54" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>146</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
@@ -2861,16 +3164,16 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55">
-      <c r="A55" s="18"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -2889,32 +3192,32 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56">
-      <c r="A56" s="18"/>
-      <c r="B56" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="F56" s="12">
+      <c r="A56" s="16"/>
+      <c r="B56" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" s="11">
         <v>1.0</v>
       </c>
-      <c r="G56" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="H56" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="I56" s="12" t="s">
+      <c r="G56" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I56" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="11" t="s">
         <v>76</v>
       </c>
       <c r="K56" s="1"/>
@@ -2935,24 +3238,24 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57">
-      <c r="A57" s="18"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="12">
+      <c r="A57" s="16"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="11">
         <v>2.0</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="H57" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="I57" s="12" t="s">
+      <c r="H57" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I57" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="J57" s="11" t="s">
         <v>79</v>
       </c>
       <c r="K57" s="1"/>
@@ -2973,24 +3276,24 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58">
-      <c r="A58" s="18"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="12">
+      <c r="A58" s="16"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="11">
         <v>3.0</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="11" t="s">
         <v>82</v>
       </c>
       <c r="K58" s="1"/>
@@ -3012,15 +3315,25 @@
     </row>
     <row r="59">
       <c r="A59" s="1"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J59" s="17" t="s">
+        <v>157</v>
+      </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3039,16 +3352,16 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60">
-      <c r="A60" s="18"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -3067,33 +3380,33 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61">
-      <c r="A61" s="18"/>
-      <c r="B61" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="F61" s="12">
+      <c r="A61" s="16"/>
+      <c r="B61" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F61" s="11">
         <v>1.0</v>
       </c>
-      <c r="G61" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="H61" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>154</v>
+      <c r="G61" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>165</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -3113,25 +3426,25 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62">
-      <c r="A62" s="18"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="12">
+      <c r="A62" s="16"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="11">
         <v>2.0</v>
       </c>
-      <c r="G62" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>157</v>
+      <c r="G62" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="J62" s="17" t="s">
+        <v>168</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -3151,16 +3464,16 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63">
-      <c r="A63" s="18"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
+      <c r="J63" s="11"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
@@ -3180,15 +3493,15 @@
     </row>
     <row r="64">
       <c r="A64" s="1"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="15"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -3207,16 +3520,16 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65">
-      <c r="A65" s="18"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -3235,33 +3548,33 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66">
-      <c r="A66" s="18"/>
-      <c r="B66" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="F66" s="12">
+      <c r="A66" s="16"/>
+      <c r="B66" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F66" s="11">
         <v>1.0</v>
       </c>
-      <c r="G66" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="H66" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>165</v>
+      <c r="G66" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>176</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -3281,25 +3594,25 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67">
-      <c r="A67" s="18"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="12">
+      <c r="A67" s="16"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="11">
         <v>2.0</v>
       </c>
-      <c r="G67" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="H67" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>165</v>
+      <c r="G67" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>180</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -3319,16 +3632,26 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68">
-      <c r="A68" s="18"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>184</v>
+      </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
@@ -3348,15 +3671,15 @@
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
-      <c r="J69" s="15"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
@@ -3375,16 +3698,16 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" ht="14.25" customHeight="1">
-      <c r="A70" s="18"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -3402,17 +3725,35 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
-      <c r="A71" s="18"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+    <row r="71" ht="56.25" customHeight="1">
+      <c r="A71" s="16"/>
+      <c r="B71" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F71" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>191</v>
+      </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -3430,17 +3771,27 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
-      <c r="A72" s="18"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
+    <row r="72" ht="56.25" customHeight="1">
+      <c r="A72" s="16"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="G72" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>195</v>
+      </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
@@ -3458,17 +3809,27 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="18"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+    <row r="73" ht="56.25" customHeight="1">
+      <c r="A73" s="16"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>199</v>
+      </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
@@ -3486,17 +3847,16 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" ht="12.0" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
+      <c r="B74" s="13"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="13"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="J74" s="11"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
@@ -3516,15 +3876,15 @@
     </row>
     <row r="75" ht="14.25" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
@@ -3542,17 +3902,35 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" ht="78.0" customHeight="1">
       <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
+      <c r="B76" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F76" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="I76" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="J76" s="21" t="s">
+        <v>206</v>
+      </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
@@ -3570,17 +3948,27 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" ht="78.0" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="J77" s="21" t="s">
+        <v>209</v>
+      </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
@@ -3598,17 +3986,17 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" ht="13.5" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
@@ -3628,15 +4016,15 @@
     </row>
     <row r="79" ht="14.25" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
+      <c r="B79" s="13"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="13"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
@@ -3656,15 +4044,15 @@
     </row>
     <row r="80" ht="14.25" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
@@ -3682,17 +4070,35 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" ht="78.0" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
+      <c r="B81" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="F81" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="I81" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="J81" s="21" t="s">
+        <v>217</v>
+      </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -3710,17 +4116,27 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" ht="78.0" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="G82" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="I82" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="J82" s="21" t="s">
+        <v>220</v>
+      </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
@@ -3738,17 +4154,27 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" ht="69.0" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="I83" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J83" s="21" t="s">
+        <v>224</v>
+      </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
@@ -3766,17 +4192,27 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" ht="65.25" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G84" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H84" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="I84" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J84" s="21" t="s">
+        <v>226</v>
+      </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
@@ -3796,15 +4232,15 @@
     </row>
     <row r="85" ht="14.25" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
+      <c r="B85" s="19"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="19"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
@@ -3822,17 +4258,35 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" ht="72.0" customHeight="1">
       <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
+      <c r="B86" s="20" t="s">
+        <v>227</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="F86" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="G86" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="I86" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="J86" s="21" t="s">
+        <v>234</v>
+      </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
@@ -3850,17 +4304,17 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="21"/>
+      <c r="I87" s="21"/>
+      <c r="J87" s="21"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
@@ -3878,17 +4332,17 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
+      <c r="J88" s="22"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -3906,17 +4360,17 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
+      <c r="B89" s="13"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="22"/>
+      <c r="I89" s="22"/>
+      <c r="J89" s="22"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
@@ -3936,15 +4390,15 @@
     </row>
     <row r="90" ht="14.25" customHeight="1">
       <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="19"/>
+      <c r="D90" s="19"/>
+      <c r="E90" s="19"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="19"/>
+      <c r="I90" s="19"/>
+      <c r="J90" s="19"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
@@ -3962,17 +4416,35 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" ht="57.75" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
+      <c r="B91" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="F91" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="G91" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="H91" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="I91" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="J91" s="21" t="s">
+        <v>242</v>
+      </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
@@ -3990,17 +4462,27 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" ht="75.0" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="G92" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="H92" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="I92" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="J92" s="21" t="s">
+        <v>245</v>
+      </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
@@ -4018,17 +4500,27 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" ht="56.25" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="G93" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="H93" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="I93" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="J93" s="21" t="s">
+        <v>248</v>
+      </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
@@ -4048,15 +4540,15 @@
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+      <c r="I94" s="22"/>
+      <c r="J94" s="22"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
@@ -4076,15 +4568,15 @@
     </row>
     <row r="95" ht="14.25" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="19"/>
+      <c r="D95" s="19"/>
+      <c r="E95" s="19"/>
+      <c r="F95" s="19"/>
+      <c r="G95" s="19"/>
+      <c r="H95" s="19"/>
+      <c r="I95" s="19"/>
+      <c r="J95" s="19"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
@@ -4102,17 +4594,35 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" ht="66.75" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
+      <c r="B96" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="F96" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="G96" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="H96" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="I96" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="J96" s="21" t="s">
+        <v>255</v>
+      </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
@@ -4130,17 +4640,27 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" ht="69.75" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="19"/>
-      <c r="J97" s="1"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="G97" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="H97" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="I97" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="J97" s="21" t="s">
+        <v>258</v>
+      </c>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
@@ -4160,15 +4680,15 @@
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="19"/>
-      <c r="J98" s="1"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="21"/>
+      <c r="J98" s="21"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
@@ -4188,15 +4708,15 @@
     </row>
     <row r="99" ht="14.25" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19"/>
-      <c r="H99" s="19"/>
-      <c r="I99" s="19"/>
-      <c r="J99" s="1"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="21"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
@@ -4216,14 +4736,14 @@
     </row>
     <row r="100" ht="14.25" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
-      <c r="G100" s="19"/>
-      <c r="H100" s="19"/>
-      <c r="I100" s="19"/>
+      <c r="B100" s="24"/>
+      <c r="C100" s="24"/>
+      <c r="D100" s="24"/>
+      <c r="E100" s="24"/>
+      <c r="F100" s="24"/>
+      <c r="G100" s="24"/>
+      <c r="H100" s="24"/>
+      <c r="I100" s="24"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -4244,14 +4764,14 @@
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="19"/>
-      <c r="G101" s="19"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="19"/>
+      <c r="B101" s="24"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="24"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="24"/>
+      <c r="I101" s="24"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -4272,14 +4792,14 @@
     </row>
     <row r="102" ht="14.25" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="20"/>
-      <c r="C102" s="20"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
+      <c r="B102" s="24"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="24"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="24"/>
+      <c r="I102" s="24"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -4300,14 +4820,14 @@
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="20"/>
-      <c r="C103" s="20"/>
-      <c r="D103" s="20"/>
-      <c r="E103" s="20"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
+      <c r="B103" s="24"/>
+      <c r="C103" s="24"/>
+      <c r="D103" s="24"/>
+      <c r="E103" s="24"/>
+      <c r="F103" s="24"/>
+      <c r="G103" s="24"/>
+      <c r="H103" s="24"/>
+      <c r="I103" s="24"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -4328,14 +4848,14 @@
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="B104" s="20"/>
-      <c r="C104" s="20"/>
-      <c r="D104" s="20"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="20"/>
-      <c r="G104" s="20"/>
-      <c r="H104" s="20"/>
-      <c r="I104" s="20"/>
+      <c r="B104" s="24"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+      <c r="I104" s="24"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -4356,14 +4876,14 @@
     </row>
     <row r="105" ht="14.25" customHeight="1">
       <c r="A105" s="1"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19"/>
-      <c r="F105" s="19"/>
-      <c r="G105" s="20"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="20"/>
+      <c r="B105" s="24"/>
+      <c r="C105" s="24"/>
+      <c r="D105" s="24"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="24"/>
+      <c r="G105" s="24"/>
+      <c r="H105" s="24"/>
+      <c r="I105" s="24"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -4384,14 +4904,14 @@
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c r="A106" s="1"/>
-      <c r="B106" s="19"/>
-      <c r="C106" s="19"/>
-      <c r="D106" s="19"/>
-      <c r="E106" s="19"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="20"/>
-      <c r="H106" s="19"/>
-      <c r="I106" s="20"/>
+      <c r="B106" s="24"/>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="24"/>
+      <c r="H106" s="24"/>
+      <c r="I106" s="24"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -4412,14 +4932,14 @@
     </row>
     <row r="107" ht="14.25" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="19"/>
-      <c r="C107" s="19"/>
-      <c r="D107" s="19"/>
-      <c r="E107" s="19"/>
-      <c r="F107" s="19"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
-      <c r="I107" s="20"/>
+      <c r="B107" s="24"/>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
+      <c r="I107" s="24"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -4440,14 +4960,14 @@
     </row>
     <row r="108" ht="14.25" customHeight="1">
       <c r="A108" s="1"/>
-      <c r="B108" s="19"/>
-      <c r="C108" s="19"/>
-      <c r="D108" s="19"/>
-      <c r="E108" s="19"/>
-      <c r="F108" s="19"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
+      <c r="B108" s="24"/>
+      <c r="C108" s="24"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="24"/>
+      <c r="H108" s="24"/>
+      <c r="I108" s="24"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -4468,14 +4988,14 @@
     </row>
     <row r="109" ht="14.25" customHeight="1">
       <c r="A109" s="1"/>
-      <c r="B109" s="19"/>
-      <c r="C109" s="19"/>
-      <c r="D109" s="19"/>
-      <c r="E109" s="19"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
+      <c r="B109" s="24"/>
+      <c r="C109" s="24"/>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="24"/>
+      <c r="H109" s="24"/>
+      <c r="I109" s="24"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -4496,14 +5016,14 @@
     </row>
     <row r="110" ht="14.25" customHeight="1">
       <c r="A110" s="1"/>
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-      <c r="D110" s="19"/>
-      <c r="E110" s="19"/>
-      <c r="F110" s="19"/>
-      <c r="G110" s="20"/>
-      <c r="H110" s="20"/>
-      <c r="I110" s="20"/>
+      <c r="B110" s="24"/>
+      <c r="C110" s="24"/>
+      <c r="D110" s="24"/>
+      <c r="E110" s="24"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="24"/>
+      <c r="H110" s="24"/>
+      <c r="I110" s="24"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -4524,14 +5044,14 @@
     </row>
     <row r="111" ht="14.25" customHeight="1">
       <c r="A111" s="1"/>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="19"/>
-      <c r="E111" s="19"/>
-      <c r="F111" s="19"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
-      <c r="I111" s="20"/>
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+      <c r="I111" s="24"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -4552,14 +5072,14 @@
     </row>
     <row r="112" ht="14.25" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="19"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
-      <c r="I112" s="20"/>
+      <c r="B112" s="24"/>
+      <c r="C112" s="24"/>
+      <c r="D112" s="24"/>
+      <c r="E112" s="24"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+      <c r="H112" s="24"/>
+      <c r="I112" s="24"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
@@ -4580,14 +5100,14 @@
     </row>
     <row r="113" ht="14.25" customHeight="1">
       <c r="A113" s="1"/>
-      <c r="B113" s="20"/>
-      <c r="C113" s="20"/>
-      <c r="D113" s="20"/>
-      <c r="E113" s="20"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
+      <c r="B113" s="24"/>
+      <c r="C113" s="24"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+      <c r="H113" s="24"/>
+      <c r="I113" s="24"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -4608,14 +5128,14 @@
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c r="A114" s="1"/>
-      <c r="B114" s="20"/>
-      <c r="C114" s="20"/>
-      <c r="D114" s="20"/>
-      <c r="E114" s="20"/>
-      <c r="F114" s="20"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="20"/>
-      <c r="I114" s="20"/>
+      <c r="B114" s="24"/>
+      <c r="C114" s="24"/>
+      <c r="D114" s="24"/>
+      <c r="E114" s="24"/>
+      <c r="F114" s="24"/>
+      <c r="G114" s="24"/>
+      <c r="H114" s="24"/>
+      <c r="I114" s="24"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
@@ -4636,14 +5156,14 @@
     </row>
     <row r="115" ht="14.25" customHeight="1">
       <c r="A115" s="1"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="20"/>
-      <c r="D115" s="20"/>
-      <c r="E115" s="20"/>
-      <c r="F115" s="20"/>
-      <c r="G115" s="20"/>
-      <c r="H115" s="20"/>
-      <c r="I115" s="20"/>
+      <c r="B115" s="24"/>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="24"/>
+      <c r="G115" s="24"/>
+      <c r="H115" s="24"/>
+      <c r="I115" s="24"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
@@ -4664,14 +5184,14 @@
     </row>
     <row r="116" ht="14.25" customHeight="1">
       <c r="A116" s="1"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="20"/>
-      <c r="D116" s="20"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="20"/>
-      <c r="G116" s="20"/>
-      <c r="H116" s="20"/>
-      <c r="I116" s="20"/>
+      <c r="B116" s="24"/>
+      <c r="C116" s="24"/>
+      <c r="D116" s="24"/>
+      <c r="E116" s="24"/>
+      <c r="F116" s="24"/>
+      <c r="G116" s="24"/>
+      <c r="H116" s="24"/>
+      <c r="I116" s="24"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
@@ -4692,14 +5212,14 @@
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="20"/>
-      <c r="C117" s="20"/>
-      <c r="D117" s="20"/>
-      <c r="E117" s="20"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
+      <c r="B117" s="24"/>
+      <c r="C117" s="24"/>
+      <c r="D117" s="24"/>
+      <c r="E117" s="24"/>
+      <c r="F117" s="24"/>
+      <c r="G117" s="24"/>
+      <c r="H117" s="24"/>
+      <c r="I117" s="24"/>
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
       <c r="L117" s="1"/>
@@ -4720,14 +5240,14 @@
     </row>
     <row r="118" ht="14.25" customHeight="1">
       <c r="A118" s="1"/>
-      <c r="B118" s="20"/>
-      <c r="C118" s="20"/>
-      <c r="D118" s="20"/>
-      <c r="E118" s="20"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="20"/>
-      <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
+      <c r="B118" s="24"/>
+      <c r="C118" s="24"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="24"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="24"/>
+      <c r="H118" s="24"/>
+      <c r="I118" s="24"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
@@ -4748,14 +5268,14 @@
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="20"/>
-      <c r="C119" s="20"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="20"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
-      <c r="I119" s="20"/>
+      <c r="B119" s="24"/>
+      <c r="C119" s="24"/>
+      <c r="D119" s="24"/>
+      <c r="E119" s="24"/>
+      <c r="F119" s="24"/>
+      <c r="G119" s="24"/>
+      <c r="H119" s="24"/>
+      <c r="I119" s="24"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
@@ -4776,14 +5296,14 @@
     </row>
     <row r="120" ht="14.25" customHeight="1">
       <c r="A120" s="1"/>
-      <c r="B120" s="20"/>
-      <c r="C120" s="20"/>
-      <c r="D120" s="20"/>
-      <c r="E120" s="20"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
-      <c r="I120" s="20"/>
+      <c r="B120" s="24"/>
+      <c r="C120" s="24"/>
+      <c r="D120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="24"/>
+      <c r="G120" s="24"/>
+      <c r="H120" s="24"/>
+      <c r="I120" s="24"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
@@ -4804,14 +5324,14 @@
     </row>
     <row r="121" ht="14.25" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="20"/>
-      <c r="C121" s="20"/>
-      <c r="D121" s="20"/>
-      <c r="E121" s="20"/>
-      <c r="F121" s="20"/>
-      <c r="G121" s="20"/>
-      <c r="H121" s="20"/>
-      <c r="I121" s="20"/>
+      <c r="B121" s="24"/>
+      <c r="C121" s="24"/>
+      <c r="D121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="24"/>
+      <c r="I121" s="24"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
@@ -4832,14 +5352,14 @@
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="20"/>
-      <c r="C122" s="20"/>
-      <c r="D122" s="20"/>
-      <c r="E122" s="20"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
+      <c r="B122" s="24"/>
+      <c r="C122" s="24"/>
+      <c r="D122" s="24"/>
+      <c r="E122" s="24"/>
+      <c r="F122" s="24"/>
+      <c r="G122" s="24"/>
+      <c r="H122" s="24"/>
+      <c r="I122" s="24"/>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
@@ -4860,14 +5380,14 @@
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="1"/>
-      <c r="B123" s="20"/>
-      <c r="C123" s="20"/>
-      <c r="D123" s="20"/>
-      <c r="E123" s="20"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
-      <c r="I123" s="20"/>
+      <c r="B123" s="24"/>
+      <c r="C123" s="24"/>
+      <c r="D123" s="24"/>
+      <c r="E123" s="24"/>
+      <c r="F123" s="24"/>
+      <c r="G123" s="24"/>
+      <c r="H123" s="24"/>
+      <c r="I123" s="24"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
@@ -4888,14 +5408,14 @@
     </row>
     <row r="124" ht="14.25" customHeight="1">
       <c r="A124" s="1"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="20"/>
-      <c r="D124" s="20"/>
-      <c r="E124" s="20"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
-      <c r="I124" s="20"/>
+      <c r="B124" s="24"/>
+      <c r="C124" s="24"/>
+      <c r="D124" s="24"/>
+      <c r="E124" s="24"/>
+      <c r="F124" s="24"/>
+      <c r="G124" s="24"/>
+      <c r="H124" s="24"/>
+      <c r="I124" s="24"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
@@ -4916,14 +5436,14 @@
     </row>
     <row r="125" ht="14.25" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="20"/>
-      <c r="C125" s="20"/>
-      <c r="D125" s="20"/>
-      <c r="E125" s="20"/>
-      <c r="F125" s="20"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
-      <c r="I125" s="20"/>
+      <c r="B125" s="24"/>
+      <c r="C125" s="24"/>
+      <c r="D125" s="24"/>
+      <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
@@ -4944,14 +5464,14 @@
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="20"/>
-      <c r="C126" s="20"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="20"/>
-      <c r="I126" s="20"/>
+      <c r="B126" s="24"/>
+      <c r="C126" s="24"/>
+      <c r="D126" s="24"/>
+      <c r="E126" s="24"/>
+      <c r="F126" s="24"/>
+      <c r="G126" s="24"/>
+      <c r="H126" s="24"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -4972,14 +5492,14 @@
     </row>
     <row r="127" ht="14.25" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="20"/>
-      <c r="C127" s="20"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="20"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="20"/>
-      <c r="I127" s="20"/>
+      <c r="B127" s="24"/>
+      <c r="C127" s="24"/>
+      <c r="D127" s="24"/>
+      <c r="E127" s="24"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="24"/>
+      <c r="H127" s="24"/>
+      <c r="I127" s="24"/>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
@@ -5000,14 +5520,14 @@
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c r="A128" s="1"/>
-      <c r="B128" s="20"/>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="20"/>
-      <c r="I128" s="20"/>
+      <c r="B128" s="24"/>
+      <c r="C128" s="24"/>
+      <c r="D128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="24"/>
+      <c r="G128" s="24"/>
+      <c r="H128" s="24"/>
+      <c r="I128" s="24"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
@@ -5028,14 +5548,14 @@
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c r="A129" s="1"/>
-      <c r="B129" s="20"/>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
-      <c r="I129" s="20"/>
+      <c r="B129" s="24"/>
+      <c r="C129" s="24"/>
+      <c r="D129" s="24"/>
+      <c r="E129" s="24"/>
+      <c r="F129" s="24"/>
+      <c r="G129" s="24"/>
+      <c r="H129" s="24"/>
+      <c r="I129" s="24"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
@@ -28911,7 +29431,7 @@
       <c r="Z981" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="79">
     <mergeCell ref="B36:B39"/>
     <mergeCell ref="B41:B44"/>
     <mergeCell ref="C41:C44"/>
@@ -28919,10 +29439,6 @@
     <mergeCell ref="E41:E44"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="C46:C49"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="E66:E69"/>
     <mergeCell ref="B51:B54"/>
     <mergeCell ref="C51:C54"/>
     <mergeCell ref="D51:D54"/>
@@ -28930,6 +29446,34 @@
     <mergeCell ref="C56:C59"/>
     <mergeCell ref="D56:D59"/>
     <mergeCell ref="E56:E59"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="C71:C74"/>
+    <mergeCell ref="D71:D74"/>
+    <mergeCell ref="E71:E74"/>
+    <mergeCell ref="D81:D84"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="B71:B74"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="D76:D79"/>
+    <mergeCell ref="E76:E79"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="B96:B99"/>
+    <mergeCell ref="C96:C99"/>
+    <mergeCell ref="D96:D99"/>
+    <mergeCell ref="E96:E99"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="C91:C94"/>
+    <mergeCell ref="D91:D94"/>
+    <mergeCell ref="E91:E94"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:J4"/>

--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.2 Épicas e Historias de Usuario/Historias Usuario con instructivo.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/2.2 Épicas e Historias de Usuario/Historias Usuario con instructivo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="259">
   <si>
     <t>Desarrollo ágil: Historias de usuario y criterios de aceptación</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Resultado / Comportamiento esperado</t>
   </si>
   <si>
-    <t>EP-01/HU-01</t>
+    <t>EP-02/HU-01</t>
   </si>
   <si>
     <t>Como nuevo usuario</t>
@@ -99,7 +99,7 @@
     <t>El sistema mostrará un mensaje erróneo comunicando que la cuenta ya se encuentra registrada</t>
   </si>
   <si>
-    <t>EP-02/HU-02</t>
+    <t>EP-01/HU-02</t>
   </si>
   <si>
     <t>Como usuario registrado</t>
@@ -111,7 +111,7 @@
     <t>para acceder a las funciones de la aplicación</t>
   </si>
   <si>
-    <t>Inicio sección exitoso</t>
+    <t>Inicio sesión exitoso</t>
   </si>
   <si>
     <t>Al iniciar sesion puede lograrse sin inconvenientes</t>
@@ -120,10 +120,10 @@
     <t>Login</t>
   </si>
   <si>
-    <t>El sistema continuará con el ingreso por PIN</t>
+    <t>El sistema continuará con el ingreso por PIN, dependiendo del PIN reconocerá usuario principal o apadrinado</t>
   </si>
   <si>
-    <t>Inicio sección ERROR</t>
+    <t>Inicio sesión ERROR</t>
   </si>
   <si>
     <t>Al iniciar sesion puede NO lograrse debido a errores de credenciales</t>
@@ -295,10 +295,10 @@
     <t>Alerta sin conexión a Internet</t>
   </si>
   <si>
-    <t>El usuario presiona el botón SOS en una zona donde el dispositivo móvil no tiene cobertura de datos o Wi-Fi.</t>
+    <t>El usuario presiona el botón SOS en una zona donde el dispositivo móvil no tiene Wi-Fi.</t>
   </si>
   <si>
-    <t>El sistema intentará enviar la alerta a través de un mensaje SMS de respaldo (fallback) a los números telefónicos registrados de los contactos.</t>
+    <t>El sistema intentará enviar la alerta al backend con su ubicación y mensaje personalizado, con esto, el backend envia notificaciones push a los contactos de emergencia del usuario</t>
   </si>
   <si>
     <t>EP-05/HU-07</t>
@@ -379,25 +379,31 @@
     <t>Creación y vinculación exitosa</t>
   </si>
   <si>
-    <t>El usuario tutor se encuentra logueado y puede añadir a un usuario externo a base de un pago</t>
+    <t>El usuario principal se encuentra logueado, tiene cupos y puede añadir a un usuario apadrinado a base del pago de un cupo</t>
   </si>
   <si>
-    <t>Pago exitoso</t>
+    <t>Vincular usuario apadrinado</t>
   </si>
   <si>
-    <t>El sistema muestra un mensaje de compra exitosa y deriva a la personalización de usuarios.</t>
+    <t xml:space="preserve">El sistema solicita el PIN del usuario principal y crea la cuenta apadrinada vinculada a la principal, con sus datos aislados para su edición. Se descuenta un cupo de usuarios apadrinados </t>
   </si>
   <si>
-    <t>Compra fallida</t>
+    <t>Sin cupos disponibles</t>
   </si>
   <si>
-    <t>El usuario tutor no pudo realizar el pago debido a fallas con la tarjeta</t>
+    <t>El usuario principal intenta comprar un cupo habiendo ya utilizado todos sus cupos de usuarios apadrinados (maximo 5)</t>
   </si>
   <si>
-    <t>Pago ERROR</t>
+    <t>El sistema no procede con el pago del cupo y muestra el mensaje "Cupo maximo de usuarios apadrinados alcanzado, no es posible la compra ni la vinculación de otro usuario. Por favor modifique y/o elimine sus usuarios apadrinados ya existentes"</t>
   </si>
   <si>
-    <t>El sistema no procede con el pago de la cuenta nueva y vuelve a darle la opción de volver a intentar.</t>
+    <t>PIN incorrecto a la creación del usuario apadrinado</t>
+  </si>
+  <si>
+    <t>El usuario principal al crear/editar un usuario apadrinado ingresa incorrectamente su PIN</t>
+  </si>
+  <si>
+    <t>El sistema rechaza la vinculación y aplica la regla de intentos</t>
   </si>
   <si>
     <t>EP-07/HU-10</t>
@@ -424,7 +430,7 @@
     <t>Validación de formato incorrecto</t>
   </si>
   <si>
-    <t>El usuario tuto intentó ingresar un pin sin respetar el formato indicado</t>
+    <t>El usuario tutor intentó ingresar un pin sin respetar el formato indicado</t>
   </si>
   <si>
     <t>El sistema solicita reintentar el ingreso del pin a guardar.</t>
@@ -437,6 +443,21 @@
   </si>
   <si>
     <t>El sistema entrega un mensaje que menciona que este usuario no podrá cambiar el PIN a menos de que la cuenta tutor desee.</t>
+  </si>
+  <si>
+    <t>PIN bloqueado por intentos</t>
+  </si>
+  <si>
+    <t>El usuario tutor ingresa tres veces un PIN incorrecto</t>
+  </si>
+  <si>
+    <t>Validación PIN</t>
+  </si>
+  <si>
+    <t>El sistema bloquea la acción por 5 minutos, el bloqueo se aplica dentro del servidor, en todos los dispositivos de la cuenta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>EP-08/HU-11</t>
@@ -459,6 +480,18 @@
   </si>
   <si>
     <t>El usuario se encuentra personalizando el texto de la alerta de antecedente médico y lo deja vacío.</t>
+  </si>
+  <si>
+    <t>Datos medicos quedan cifrados</t>
+  </si>
+  <si>
+    <t>Se tratan de ver los datos medicos por alguien que no se el usuario o sus contactos de emergencia.</t>
+  </si>
+  <si>
+    <t>Cifrado de datos medicos</t>
+  </si>
+  <si>
+    <t>El sistema hace un cifrado de los datos o los oculta ante personas no autorizadas.</t>
   </si>
   <si>
     <t>EP-08/HU-12</t>
@@ -491,7 +524,7 @@
     <t>El sistema no encuentra información relevante increada del usuario</t>
   </si>
   <si>
-    <t>El sistema debe poder enviar una alerta de emergencia con información importante, si no llegase haber información relevante el usuario no podrá enviar un mensaje de emergencia</t>
+    <t>El sistema debe poder enviar una alerta de emergencia con información importante, si no llegase haber información relevante, se enviara un mensaje generico de emergencia.</t>
   </si>
   <si>
     <t>EP-09/HU-13</t>
@@ -507,19 +540,40 @@
 </t>
   </si>
   <si>
-    <t>Generar un CRUD de los usuarios y sus usuarios apadrinados</t>
+    <t>Listar y filtrar cuentas</t>
   </si>
   <si>
-    <t>Se debe poder modificar, eliminar, agregar y buscar datos relevantes para caso de inconvenientes técnicos</t>
+    <t>El administrador está autenticado con el rol "Administador" en el panel</t>
   </si>
   <si>
-    <t>CRUD</t>
+    <t>Buscar cuentas</t>
   </si>
   <si>
-    <t>El sistema debe entregar la información actualizada a tiempo real</t>
+    <t xml:space="preserve">El sistema lista las cuentas principales y apadrinadas con su correo, estado, nivel de acceso, acciones y alertas, sin mostrar información medica </t>
   </si>
   <si>
-    <t xml:space="preserve">Generar un CRUD de los datos de compra de los usuarios </t>
+    <t>Cambiar estado o rol de una cuenta</t>
+  </si>
+  <si>
+    <t>El administrador bloquea, reactiva o cambia el rol (dependiendo del caso) de una cuenta distinta de la suya</t>
+  </si>
+  <si>
+    <t>Gestionar cuenta</t>
+  </si>
+  <si>
+    <t>El sistema aplica el cambio, lo registra en la bitácora. Si se intenta cambiar el rol del mismo administrador se rechaza el cambio</t>
+  </si>
+  <si>
+    <t>Consulta de compras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El administrador consulta las compras realizadas en el sistema o de un usuario </t>
+  </si>
+  <si>
+    <t>Consultar compras</t>
+  </si>
+  <si>
+    <t>El sistema muestra las ventas solo en modo lectura, estas no pueden ser ni modificadas ni eliminadas</t>
   </si>
   <si>
     <t>EP-05/HU-14</t>
@@ -540,31 +594,208 @@
     <t>El usuario tiene una alerta ACTIVA y ya puede finalizar la misma por su propia cuenta</t>
   </si>
   <si>
+    <t>El sistema pide una confirmación, cambia el estado a FINALIZADA y revoca el acceso medico e informa a los contactos que la situación terminó</t>
+  </si>
+  <si>
     <t>Expiración automatica</t>
+  </si>
+  <si>
+    <t>Una alerta sigue ACTIVA pasadas 24 horas desde su activación</t>
   </si>
   <si>
     <t>Tarea automatica</t>
   </si>
   <si>
+    <t>El sistema cambia el estado a EXPIRADA y revoca el enlace a información medica</t>
+  </si>
+  <si>
     <t>Emergencia ya cerrada</t>
+  </si>
+  <si>
+    <t>El usuario intenta cerrar una alerta ya finalizada</t>
   </si>
   <si>
     <t>Alerta finalizada</t>
   </si>
   <si>
+    <t>El sistema rechaza la acción, entregando el mensaje "La emergencia ya fue cerrada", sin cambiar el estado de la misma</t>
+  </si>
+  <si>
     <t>EP-02/HU-15</t>
+  </si>
+  <si>
+    <t>quiero modificar mis credenciales de inicio de sesión (contraseña)</t>
+  </si>
+  <si>
+    <t>para mantener mis credenciales de acceso y perfil actualizadas</t>
+  </si>
+  <si>
+    <t>Cambio de contraseña exitoso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario autenticado solicita un cambio de contraseña mediante recuperación por correo electronico e ingresa contraseña con el formato adecuado </t>
+  </si>
+  <si>
+    <t>Actualizar credenciales</t>
+  </si>
+  <si>
+    <t>El sistema guarda el hash de la contraseña y confirma el cambio</t>
+  </si>
+  <si>
+    <t>Cambio de contraseña erroneo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario autenticado solicita un cambio de contraseña mediante recuperación por correo electronico e ingresa contraseña con el formato incorrecto </t>
+  </si>
+  <si>
+    <t>El sistema rechaza el cambio con el mensaje "No fue posible cambiar la contraseña. Verifique el formato ingresado"</t>
   </si>
   <si>
     <t>EP-07/HU-16</t>
   </si>
   <si>
+    <t>Como usuario principal</t>
+  </si>
+  <si>
+    <t>quiero comprar un plan o cupos para usuarios apadrinados desde la aplicación web</t>
+  </si>
+  <si>
+    <t>para acceder a las funciones principales del sistema y/o ampliar la protección a mis dependientes</t>
+  </si>
+  <si>
+    <t>Pago exitoso de cupos</t>
+  </si>
+  <si>
+    <t>El usuario se encuentra logeado, tiene plan, tiene cupos disponibles para añadir un usuario apadrinado, y añade un cupo mediante un pago por la pasarela de pagos</t>
+  </si>
+  <si>
+    <t>Pago exitoso</t>
+  </si>
+  <si>
+    <t>El sistema muestra el mensaje "La compra fue realizada exitosamente" y registra el cupo en la cuenta del usuario principal</t>
+  </si>
+  <si>
+    <t>Pago exitoso de plan</t>
+  </si>
+  <si>
+    <t>El usuario se encuentra logeado, no tiene plan y adquiere uno mediante un pago por la pasarela de pagos</t>
+  </si>
+  <si>
+    <t>El sistema muestra el mensaje "La compra fue realizada exitosamente" y convierte al usuario en usuario principal, habilitando las funciones principales del sistema de alertas</t>
+  </si>
+  <si>
+    <t>Pago rechazado</t>
+  </si>
+  <si>
+    <t>El usuario no pudo realizar el pago debido a fallos en ingreso de datos</t>
+  </si>
+  <si>
+    <t>Pago erroneo</t>
+  </si>
+  <si>
+    <t>El sistema no procede con el pago y muestra el mensaje "El formato de datos de pagos ingresado es erroneo, por favor intenta nuevamente"</t>
+  </si>
+  <si>
+    <t>El usuario no pudo realizar el pago debido a fallos de la pasarela de pago</t>
+  </si>
+  <si>
+    <t>El sistema no procede con el pago y muestra el mensaje "La pasarela de pagos está inhabilitada temporalmente, por favor intente nuevamente mas tarde"</t>
+  </si>
+  <si>
     <t>EP-04/HU-17</t>
+  </si>
+  <si>
+    <t>Como usuario principal/apadrinado</t>
+  </si>
+  <si>
+    <t>quiero ver los números oficiales de emergencia con acceso directo a llamada</t>
+  </si>
+  <si>
+    <t>para contactar rapidamente a los servicios publicos de emergencia al momento de una alerta</t>
+  </si>
+  <si>
+    <t>Llamar a un número oficial</t>
+  </si>
+  <si>
+    <t>El usuario, al generar una alerta en la aplicación movil, puede llamar directamente a los servicios de emergencia</t>
+  </si>
+  <si>
+    <t>Números oficiales</t>
+  </si>
+  <si>
+    <t>El sistema muestra los numeros de emergencia (131, 132, 133) con un acceso directo de llamada directa, nunca realizando llamados automaticos a dichos servicios</t>
   </si>
   <si>
     <t>EP-09/HU-18</t>
   </si>
   <si>
+    <t>Como usuario o visitante</t>
+  </si>
+  <si>
+    <t>quiero enviar una solicitud de soporte</t>
+  </si>
+  <si>
+    <t>para recibir ayuda ante problemas con la aplicación</t>
+  </si>
+  <si>
+    <t>Solicitud valida (usuario registrado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario completa el formulario de solicitud con categoría y descripción, esta incluye su nombre de usuario y correo </t>
+  </si>
+  <si>
+    <t>Enviar solicitud</t>
+  </si>
+  <si>
+    <t>El sistema crea el ticket, muestra el identificador de la solicitud y el estado inicial de la misma</t>
+  </si>
+  <si>
+    <t>Solicitud valida (usuario visitante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario completa el formulario de solicitud con categoría y descripción, redactando el mismo su nombre y correo electronico para una posterior respuesta </t>
+  </si>
+  <si>
+    <t>El sistema crea el ticket, muestra el identificador de la solicitud y el estado inicial de la misma mediante correo electronico</t>
+  </si>
+  <si>
+    <t>Formulario incompleto</t>
+  </si>
+  <si>
+    <t>El usuario, al redactar el formulario,omite un campo obligatorio o ingresa un correo invalido</t>
+  </si>
+  <si>
+    <t>El sistema no envia la solicitud y muestra el mensaje "El formulario está incorrecto, por favor verifique los campos obligatorios y/o el correo ingresado"</t>
+  </si>
+  <si>
     <t>EP-09/HU-19</t>
+  </si>
+  <si>
+    <t>quiero generar un informe de la actividad de mi cuenta y los usuarios apadrinados</t>
+  </si>
+  <si>
+    <t>para revisar el historial de alertas y acciones</t>
+  </si>
+  <si>
+    <t>Informe con datos</t>
+  </si>
+  <si>
+    <t>El usuario principal solicita un informe de actividades, cuando tanto alertas como acciones dentro de su cuenta o los usuarios apadrinados fueron realizadas</t>
+  </si>
+  <si>
+    <t>Generar informe</t>
+  </si>
+  <si>
+    <t>El sistema genera un PDF solo con la actividad de su cuenta y de sus apadrinados</t>
+  </si>
+  <si>
+    <t>Sin datos de historial</t>
+  </si>
+  <si>
+    <t>El usuario principal solicita un informe de actividades, cuando tanto alertas como acciones NO se han realizado dentro de su cuenta o los usuarios apadrinados</t>
+  </si>
+  <si>
+    <t>El sistema informa "No existen registros para realizar un informe correctamente" y evita la descarga del mismo</t>
   </si>
 </sst>
 </file>
@@ -786,23 +1017,23 @@
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="7" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -2654,10 +2885,10 @@
         <v>124</v>
       </c>
       <c r="I47" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J47" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2682,11 +2913,21 @@
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
+      <c r="F48" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -2763,31 +3004,31 @@
     <row r="51">
       <c r="A51" s="16"/>
       <c r="B51" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>116</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F51" s="11">
         <v>1.0</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2816,16 +3057,16 @@
         <v>2.0</v>
       </c>
       <c r="G52" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="I52" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="H52" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I52" s="11" t="s">
-        <v>132</v>
-      </c>
       <c r="J52" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2854,16 +3095,16 @@
         <v>3.0</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2882,18 +3123,30 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" ht="45.0" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
       <c r="E54" s="13"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="1"/>
+      <c r="F54" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="G54" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="H54" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="I54" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="J54" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="K54" s="18" t="s">
+        <v>146</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
@@ -2941,25 +3194,25 @@
     <row r="56">
       <c r="A56" s="16"/>
       <c r="B56" s="10" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F56" s="11">
         <v>1.0</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I56" s="11" t="s">
         <v>75</v>
@@ -2997,7 +3250,7 @@
         <v>77</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="I57" s="11" t="s">
         <v>75</v>
@@ -3066,11 +3319,21 @@
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
       <c r="E59" s="13"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="11"/>
-      <c r="H59" s="11"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="11"/>
+      <c r="F59" s="17">
+        <v>4.0</v>
+      </c>
+      <c r="G59" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J59" s="17" t="s">
+        <v>157</v>
+      </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3119,31 +3382,31 @@
     <row r="61">
       <c r="A61" s="16"/>
       <c r="B61" s="10" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F61" s="11">
         <v>1.0</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -3172,16 +3435,16 @@
         <v>2.0</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="J62" s="11" t="s">
-        <v>157</v>
+        <v>164</v>
+      </c>
+      <c r="J62" s="17" t="s">
+        <v>168</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -3287,31 +3550,31 @@
     <row r="66">
       <c r="A66" s="16"/>
       <c r="B66" s="10" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F66" s="11">
         <v>1.0</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -3340,16 +3603,16 @@
         <v>2.0</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -3374,11 +3637,21 @@
       <c r="C68" s="12"/>
       <c r="D68" s="12"/>
       <c r="E68" s="12"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="11"/>
-      <c r="I68" s="11"/>
-      <c r="J68" s="11"/>
+      <c r="F68" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>184</v>
+      </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
@@ -3452,33 +3725,35 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" ht="53.25" customHeight="1">
+    <row r="71" ht="56.25" customHeight="1">
       <c r="A71" s="16"/>
-      <c r="B71" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C71" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D71" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="E71" s="17" t="s">
-        <v>170</v>
+      <c r="B71" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="F71" s="11">
         <v>1.0</v>
       </c>
-      <c r="G71" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="H71" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="I71" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="J71" s="11"/>
+      <c r="G71" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>191</v>
+      </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -3496,7 +3771,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" ht="46.5" customHeight="1">
+    <row r="72" ht="56.25" customHeight="1">
       <c r="A72" s="16"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -3505,14 +3780,18 @@
       <c r="F72" s="11">
         <v>2.0</v>
       </c>
-      <c r="G72" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="H72" s="11"/>
-      <c r="I72" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="J72" s="11"/>
+      <c r="G72" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>195</v>
+      </c>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
@@ -3530,23 +3809,27 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" ht="42.75" customHeight="1">
+    <row r="73" ht="56.25" customHeight="1">
       <c r="A73" s="16"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
       <c r="D73" s="12"/>
       <c r="E73" s="12"/>
-      <c r="F73" s="18">
+      <c r="F73" s="11">
         <v>3.0</v>
       </c>
-      <c r="G73" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="H73" s="11"/>
-      <c r="I73" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="J73" s="11"/>
+      <c r="G73" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="I73" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>199</v>
+      </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
@@ -3564,13 +3847,13 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" ht="45.75" customHeight="1">
+    <row r="74" ht="12.0" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
       <c r="D74" s="13"/>
       <c r="E74" s="13"/>
-      <c r="F74" s="18"/>
+      <c r="F74" s="11"/>
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="J74" s="11"/>
@@ -3619,34 +3902,34 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" ht="78.0" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E76" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="F76" s="22">
+        <v>200</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F76" s="21">
         <v>1.0</v>
       </c>
-      <c r="G76" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="H76" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I76" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J76" s="22" t="s">
-        <v>165</v>
+      <c r="G76" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="I76" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="J76" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -3665,26 +3948,26 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" ht="78.0" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="12"/>
       <c r="E77" s="12"/>
-      <c r="F77" s="22">
+      <c r="F77" s="21">
         <v>2.0</v>
       </c>
-      <c r="G77" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="H77" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I77" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J77" s="22" t="s">
-        <v>165</v>
+      <c r="G77" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="J77" s="21" t="s">
+        <v>209</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -3703,17 +3986,17 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" ht="13.5" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
       <c r="D78" s="12"/>
       <c r="E78" s="12"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="23"/>
+      <c r="F78" s="22"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="22"/>
+      <c r="J78" s="22"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
@@ -3737,11 +4020,11 @@
       <c r="C79" s="13"/>
       <c r="D79" s="13"/>
       <c r="E79" s="13"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="23"/>
+      <c r="F79" s="22"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="22"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
@@ -3787,34 +4070,34 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" ht="78.0" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E81" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="F81" s="22">
+        <v>210</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="F81" s="21">
         <v>1.0</v>
       </c>
-      <c r="G81" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="H81" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I81" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J81" s="22" t="s">
-        <v>165</v>
+      <c r="G81" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="I81" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="J81" s="21" t="s">
+        <v>217</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -3833,26 +4116,26 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" ht="78.0" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
       <c r="D82" s="12"/>
       <c r="E82" s="12"/>
-      <c r="F82" s="22">
+      <c r="F82" s="21">
         <v>2.0</v>
       </c>
-      <c r="G82" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="H82" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I82" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J82" s="22" t="s">
-        <v>165</v>
+      <c r="G82" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="I82" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="J82" s="21" t="s">
+        <v>220</v>
       </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -3871,17 +4154,27 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" ht="69.0" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
       <c r="D83" s="12"/>
       <c r="E83" s="12"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="23"/>
-      <c r="H83" s="23"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="23"/>
+      <c r="F83" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="I83" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J83" s="21" t="s">
+        <v>224</v>
+      </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
@@ -3899,17 +4192,27 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" ht="65.25" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="13"/>
       <c r="C84" s="13"/>
       <c r="D84" s="13"/>
       <c r="E84" s="13"/>
-      <c r="F84" s="23"/>
-      <c r="G84" s="23"/>
-      <c r="H84" s="23"/>
-      <c r="I84" s="23"/>
-      <c r="J84" s="23"/>
+      <c r="F84" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G84" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="H84" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="I84" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="J84" s="21" t="s">
+        <v>226</v>
+      </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
@@ -3955,34 +4258,34 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" ht="72.0" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D86" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E86" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="F86" s="22">
+        <v>227</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="F86" s="21">
         <v>1.0</v>
       </c>
-      <c r="G86" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="H86" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I86" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J86" s="22" t="s">
-        <v>165</v>
+      <c r="G86" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="H86" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="I86" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="J86" s="21" t="s">
+        <v>234</v>
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -4001,27 +4304,17 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
       <c r="D87" s="12"/>
       <c r="E87" s="12"/>
-      <c r="F87" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="G87" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="H87" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I87" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J87" s="22" t="s">
-        <v>165</v>
-      </c>
+      <c r="F87" s="21"/>
+      <c r="G87" s="21"/>
+      <c r="H87" s="21"/>
+      <c r="I87" s="21"/>
+      <c r="J87" s="21"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
@@ -4039,17 +4332,17 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
       <c r="D88" s="12"/>
       <c r="E88" s="12"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="23"/>
-      <c r="J88" s="23"/>
+      <c r="F88" s="22"/>
+      <c r="G88" s="22"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="22"/>
+      <c r="J88" s="22"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
@@ -4067,17 +4360,17 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="13"/>
       <c r="C89" s="13"/>
       <c r="D89" s="13"/>
       <c r="E89" s="13"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="23"/>
-      <c r="J89" s="23"/>
+      <c r="F89" s="22"/>
+      <c r="G89" s="22"/>
+      <c r="H89" s="22"/>
+      <c r="I89" s="22"/>
+      <c r="J89" s="22"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
@@ -4123,34 +4416,34 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" ht="57.75" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="C91" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D91" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E91" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="F91" s="22">
+        <v>235</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="D91" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="F91" s="21">
         <v>1.0</v>
       </c>
-      <c r="G91" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="H91" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I91" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J91" s="22" t="s">
-        <v>165</v>
+      <c r="G91" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="H91" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="I91" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="J91" s="21" t="s">
+        <v>242</v>
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
@@ -4169,26 +4462,26 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" ht="75.0" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
       <c r="D92" s="12"/>
       <c r="E92" s="12"/>
-      <c r="F92" s="22">
+      <c r="F92" s="21">
         <v>2.0</v>
       </c>
-      <c r="G92" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="H92" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I92" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J92" s="22" t="s">
-        <v>165</v>
+      <c r="G92" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="H92" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="I92" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="J92" s="21" t="s">
+        <v>245</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -4207,17 +4500,27 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" ht="56.25" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
       <c r="D93" s="12"/>
       <c r="E93" s="12"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="23"/>
-      <c r="J93" s="23"/>
+      <c r="F93" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="G93" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="H93" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="I93" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="J93" s="21" t="s">
+        <v>248</v>
+      </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
@@ -4241,11 +4544,11 @@
       <c r="C94" s="13"/>
       <c r="D94" s="13"/>
       <c r="E94" s="13"/>
-      <c r="F94" s="23"/>
-      <c r="G94" s="23"/>
-      <c r="H94" s="23"/>
-      <c r="I94" s="23"/>
-      <c r="J94" s="23"/>
+      <c r="F94" s="22"/>
+      <c r="G94" s="22"/>
+      <c r="H94" s="22"/>
+      <c r="I94" s="22"/>
+      <c r="J94" s="22"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
@@ -4291,34 +4594,34 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" ht="66.75" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D96" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E96" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="F96" s="22">
+        <v>249</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D96" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="F96" s="21">
         <v>1.0</v>
       </c>
-      <c r="G96" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="H96" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I96" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J96" s="22" t="s">
-        <v>165</v>
+      <c r="G96" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="H96" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="I96" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="J96" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -4337,26 +4640,26 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" ht="69.75" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
       <c r="D97" s="12"/>
       <c r="E97" s="12"/>
-      <c r="F97" s="22">
+      <c r="F97" s="21">
         <v>2.0</v>
       </c>
-      <c r="G97" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="H97" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="I97" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="J97" s="22" t="s">
-        <v>165</v>
+      <c r="G97" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="H97" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="I97" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="J97" s="21" t="s">
+        <v>258</v>
       </c>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
@@ -4381,11 +4684,11 @@
       <c r="C98" s="12"/>
       <c r="D98" s="12"/>
       <c r="E98" s="12"/>
-      <c r="F98" s="23"/>
-      <c r="G98" s="23"/>
-      <c r="H98" s="23"/>
-      <c r="I98" s="23"/>
-      <c r="J98" s="23"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="21"/>
+      <c r="J98" s="21"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
@@ -4409,11 +4712,11 @@
       <c r="C99" s="13"/>
       <c r="D99" s="13"/>
       <c r="E99" s="13"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="23"/>
-      <c r="H99" s="23"/>
-      <c r="I99" s="23"/>
-      <c r="J99" s="23"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="21"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
